--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -601,7 +601,7 @@
         <v>43955</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45791</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44789</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44931</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45153</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45093</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>45471</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45103</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>44630</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>44762</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45594</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44645</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>44762</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>45973</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>46071</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>46253</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>45230</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>44676</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44655</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>45884</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>45588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>45741</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>46188</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44998</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44888</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>45152</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44039</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>44657</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>44756</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>44957</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>45357</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>45194</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44980</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>46175</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>45559</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>46182</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>46181</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>46091</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>46133</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>44973</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45717</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45012</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>45063</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>46252</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45559</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>45457</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45699</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>45545</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>46139</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>44546</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>44825</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>44649</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44880</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44630</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>44860</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44880</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>44676</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>44510</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>44504</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>44848</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>44827</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44581</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44592</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44753</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44845</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44462</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44790</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>44608</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>44860</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>44693</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44762</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>44825</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>44825</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>44565</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44503</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44490</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>44474</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44468</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>44596</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>44576</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>44721</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>44762</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>44762</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44882</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44532</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>44494</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>44806</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>44501</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44518</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44845</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>44872</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>44886</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>44630</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44694</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>44504</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44853</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>44817</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44638</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44812</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44637</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44539</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>44586</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44713</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>44762</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>44494</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>44627</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44630</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45706</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45432</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>44903</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>45251</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45121</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>45012</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44903</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>45071</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44617</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>45747</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>45261</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44987</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45196</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45328</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45621</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>45012</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45602</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45341</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>45600</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44987</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>45310</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>44627</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>45328</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>45238</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>45551</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>45600</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>45128</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>45588</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>44944</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45691</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45363</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>45482</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45670</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>45503</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>45739</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>44987</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>44987</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45061</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>45432</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>45201</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45201</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>45115</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>45169</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>44908</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>45098</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>45147</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>45012</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>44880</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>44822</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>45719</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>45426</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>45440</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>45169</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>45299</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44884</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>44754</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>44600</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>45043</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>45402</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>45646</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>45006</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45099</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>45719</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>45118</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>45754</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>45192</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>45646</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>45714</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>45225</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>45280</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>45360</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>45559</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>45743</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>45560</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>45460</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45670</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>45932</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>45929</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45891</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>45891</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>45673</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45440</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>45104</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>44939</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>46139</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>45888</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45889</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>45888</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45280</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45280</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45889</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45821</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>45757</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>45104</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>45892</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45964</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>45111</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>45954</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>44848</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44916</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>45387</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>45889</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45807</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45903</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45889</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45841</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>44966</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45749</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>45743</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45505</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45843</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45807</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>45266</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45616</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>45910</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>45053</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>46140</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>46140</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45910</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>46140</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>45915</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>46140</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>45915</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45915</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45915</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45915</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>45915</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45706</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>45429</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>45775</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>45597</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>45918</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>45918</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>45630</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>45630</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>44944</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>45019</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>45923</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>44722</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>45925</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>44756</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>45085</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>45706</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>45012</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>45462</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>44966</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>45272</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>45932</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>45932</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>45299</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>45932</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45432</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>44966</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>45001</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>45001</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>45505</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45937</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45937</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>46147</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>45359</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>45090</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45589</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>45194</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>44917</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45168</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45071</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>46149</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45597</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>45197</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>45947</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>46149</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>45099</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>45950</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>45360</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>44565</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>45951</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44980</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>44586</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>45954</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>45610</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>44595</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>44754</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>44753</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>45166</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45001</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45646</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45002</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45460</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>45246</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>45299</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>45001</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>45036</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>45357</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45054</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45555</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45394</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>45581</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>45402</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>45381</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45169</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>45354</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>45974</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45975</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45978</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>45009</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>45009</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>45978</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>45702</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>45981</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>45588</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>45841</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>45986</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>45986</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>45278</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26202,7 +26202,7 @@
         <v>45992</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26275,7 +26275,7 @@
         <v>45602</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>45754</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>44987</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>45117</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45646</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45480</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45302</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>45327</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>44729</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>46162</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>45995</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>45619</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>45855</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>46162</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>45995</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>46162</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>45714</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>46000</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>45337</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>44917</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>46164</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>46007</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>46007</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44739</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>44778</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>44494</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>44973</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44966</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>44489</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>44762</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>46168</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>44739</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>44753</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>46168</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>44862</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28840,7 +28840,7 @@
         <v>45470</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>45086</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>45310</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>45040</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29132,7 +29132,7 @@
         <v>45757</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29205,7 +29205,7 @@
         <v>46171</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>44829</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>44956</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29429,7 +29429,7 @@
         <v>45166</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>44882</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29575,7 +29575,7 @@
         <v>45534</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29648,7 +29648,7 @@
         <v>44893</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29721,7 +29721,7 @@
         <v>45610</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>44972</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>44882</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29940,7 +29940,7 @@
         <v>45009</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>45062</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>46042</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>45316</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>45342</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>46046</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>46048</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>46050</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>44713</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>46052</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>46052</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>45426</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         <v>45588</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>45194</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>44817</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>46059</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>46059</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>45559</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>45328</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>45328</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>45360</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>45360</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>45104</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>46182</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>45775</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>46066</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>46181</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>46181</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45105</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>46069</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45075</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>46071</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>44945</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>46071</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>46182</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>44606</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>46181</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>46073</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>46073</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>46078</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>46078</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>46077</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>46078</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45178</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>45068</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>45536</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33353,7 +33353,7 @@
         <v>46078</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>46078</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>46184</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>46184</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>46079</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33718,7 +33718,7 @@
         <v>46079</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>46079</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>46079</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45072</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>46086</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>46086</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>45196</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>45195</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>45082</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>45193</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>45264</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34536,7 +34536,7 @@
         <v>45085</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>45091</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>46195</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>46104</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>46104</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34901,7 +34901,7 @@
         <v>46104</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34974,7 +34974,7 @@
         <v>46105</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>46199</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>45921</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>45110</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>45152</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>45139</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>45169</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35485,7 +35485,7 @@
         <v>46198</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>46104</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>45118</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>46112</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35777,7 +35777,7 @@
         <v>45178</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35850,7 +35850,7 @@
         <v>45062</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35928,7 +35928,7 @@
         <v>45201</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>45195</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>45027</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45602</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
         <v>46119</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>46199</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45378</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45436</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>45350</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>45350</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>45303</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>45303</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36804,7 +36804,7 @@
         <v>46202</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>46126</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>44974</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>44806</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37096,7 +37096,7 @@
         <v>46202</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37169,7 +37169,7 @@
         <v>44992</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>45246</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>46133</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44565</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37461,7 +37461,7 @@
         <v>45237</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>44774</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>45545</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45303</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>45430</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>46062</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45625</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>44956</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38045,7 +38045,7 @@
         <v>45342</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45342</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38191,7 +38191,7 @@
         <v>45428</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38264,7 +38264,7 @@
         <v>45677</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>44992</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>46139</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>45811</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>45373</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45724</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>46247</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>44651</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38858,7 +38858,7 @@
         <v>45560</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>45408</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39009,7 +39009,7 @@
         <v>45097</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>45189</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
         <v>45051</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>45006</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39301,7 +39301,7 @@
         <v>45139</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>46205</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45076</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>44819</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>44658</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>46248</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39739,7 +39739,7 @@
         <v>46210</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>46252</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>45685</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>46209</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>46210</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>45545</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40177,7 +40177,7 @@
         <v>45119</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>46253</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45201</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>44992</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>45063</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>46209</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40630,7 +40630,7 @@
         <v>44748</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>46168</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>46212</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40849,7 +40849,7 @@
         <v>46212</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40922,7 +40922,7 @@
         <v>45078</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40995,7 +40995,7 @@
         <v>46140</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>45327</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>45600</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41214,7 +41214,7 @@
         <v>44466</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>44980</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>44950</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45722</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>46216</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>45058</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>45560</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41735,7 +41735,7 @@
         <v>45194</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>46209</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41881,7 +41881,7 @@
         <v>46218</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45057</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42027,7 +42027,7 @@
         <v>46259</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>46259</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45012</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>45012</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>46261</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>44902</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>46261</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45238</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42611,7 +42611,7 @@
         <v>46265</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42684,7 +42684,7 @@
         <v>46265</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>46265</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>46265</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>45545</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42981,7 +42981,7 @@
         <v>46268</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45229</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43127,7 +43127,7 @@
         <v>46267</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43200,7 +43200,7 @@
         <v>46226</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>45104</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43351,7 +43351,7 @@
         <v>46268</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43424,7 +43424,7 @@
         <v>45104</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43502,7 +43502,7 @@
         <v>45574</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>45527</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43648,7 +43648,7 @@
         <v>46267</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>45531</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>45560</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43867,7 +43867,7 @@
         <v>45691</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43940,7 +43940,7 @@
         <v>45394</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45608</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>44966</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>45104</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
         <v>45502</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44310,7 +44310,7 @@
         <v>46272</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44383,7 +44383,7 @@
         <v>46272</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45785</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>46229</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>46265</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45567</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>46279</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44836,7 +44836,7 @@
         <v>46279</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>45527</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>45546</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>46276</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45724</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45579</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45530</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>45646</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>45562</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>45551</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>45280</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>46281</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45791</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45672</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>44973</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>45078</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45597</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46092,7 +46092,7 @@
         <v>45194</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>45247</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45579</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>45490</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46384,7 +46384,7 @@
         <v>45803</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
         <v>45785</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45813</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>45413</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45827</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46759,7 +46759,7 @@
         <v>45827</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45825</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>45833</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46983,7 +46983,7 @@
         <v>45835</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>45835</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45838</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>45838</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>45840</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47348,7 +47348,7 @@
         <v>45843</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>45537</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45846</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45846</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47640,7 +47640,7 @@
         <v>45856</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45653</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45715</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47859,7 +47859,7 @@
         <v>44474</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>44755</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>44608</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48078,7 +48078,7 @@
         <v>44986</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>44483</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>45485</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>45646</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>45602</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45573</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>45656</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>44959</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45457</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         <v>45154</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45154</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>46050</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>46064</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>46099</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -601,7 +601,7 @@
         <v>43955</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45791</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44789</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44931</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45153</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45103</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>45471</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45093</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>44630</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>44762</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45594</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44645</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>44762</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>46071</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>45973</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>46253</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>45230</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>44676</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45884</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>44655</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>44998</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>44888</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>45152</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>45588</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>46188</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>45741</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44039</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>44657</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>44756</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>44957</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>45545</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>46091</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44973</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>45012</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>46133</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>45357</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>45559</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>46175</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>46181</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>46182</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45063</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>46252</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>45194</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>44980</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45559</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>45717</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45457</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>45699</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>46139</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>44546</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>44825</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>44880</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44649</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44630</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>44860</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44880</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>44676</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>44510</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>44504</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>44848</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>44827</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44592</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44581</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44753</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44845</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44790</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44608</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>44693</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>44860</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44762</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>44825</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>44565</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>44503</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44490</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44474</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>44468</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44596</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>44576</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>44721</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>44762</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44762</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44882</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44532</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44494</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>44806</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>44518</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>44501</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44845</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44872</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>44886</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>44630</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>44694</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44504</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>44853</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44817</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>44638</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44812</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44637</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44539</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44586</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>44713</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44762</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44494</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>44627</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>44630</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45719</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45621</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45196</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>44778</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>45360</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>45051</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>45536</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>45310</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>44893</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>45378</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>44806</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>45342</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>45342</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>45238</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>45426</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>45381</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>45754</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11603,7 +11603,7 @@
         <v>45086</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>45261</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>45121</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>44903</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
         <v>45505</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>45099</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>44884</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44817</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>44939</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>45328</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>44595</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44944</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>45012</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>44980</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45888</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>45757</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>45597</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>45672</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>45889</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>45888</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>45889</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>45892</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>44973</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>45194</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>45619</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>45303</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>45078</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45597</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>46048</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>45646</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>45426</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>46046</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>45807</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>45280</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>45589</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>46050</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>44992</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>46052</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>45559</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45841</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>46052</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>45247</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45749</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>45743</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>45807</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45910</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>45843</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45910</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>44903</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>45387</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>45915</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>44627</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>45616</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>45178</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45915</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45915</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>45915</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>45602</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>45915</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         <v>45915</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>46059</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>46059</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>45918</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>45551</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>45918</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>45579</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>44489</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>46066</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         <v>44565</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>46069</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         <v>45803</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>45490</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>45923</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>46071</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>45104</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>46071</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>45505</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>46073</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>45192</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45194</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>46073</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45925</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45706</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>46078</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>46078</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>46078</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>46079</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>46079</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>46079</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>46078</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>46078</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45932</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>45932</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>45197</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>45785</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45722</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45932</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>46086</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>46086</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>45588</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44944</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45937</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>45937</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45071</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45054</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45238</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45091</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44754</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45947</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>45950</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45739</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>46105</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>46104</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45559</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>46104</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>46104</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45951</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45068</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>45954</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45280</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>46104</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45085</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45009</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>45009</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>46112</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45012</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>44966</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45299</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>46119</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>45328</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>45328</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45009</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>46126</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>45480</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45328</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45813</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45974</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>45061</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44713</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>45978</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45975</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>45978</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>46133</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45166</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>45981</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>45001</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45811</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>45986</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>45986</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>45646</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>45964</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>45178</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>45677</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>45932</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         <v>45757</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>45821</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         <v>45117</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         <v>45673</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45992</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45903</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>45929</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>45560</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>45440</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>45625</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>44992</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45954</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45670</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45889</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45855</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45889</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44966</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45995</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>44822</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>46000</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>46140</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>46140</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>45891</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>45891</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>46139</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>44987</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>44739</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>46007</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>46007</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25132,7 +25132,7 @@
         <v>46062</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>45706</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>45482</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>45085</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>45193</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>45194</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>46140</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>45555</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>45413</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44748</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>45743</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>46139</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>46140</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>45754</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>44916</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45825</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>44862</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>45827</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>45827</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>45264</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>44917</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>45090</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>46147</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>46149</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>46149</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>44882</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44466</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>45266</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>44880</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45196</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>45600</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>45833</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>45838</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>45838</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>45835</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45835</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>45436</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>44966</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>45646</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>45303</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>45303</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>45840</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28223,7 +28223,7 @@
         <v>46162</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>45194</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>45841</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>45118</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>46162</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>46162</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>45341</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>45168</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>45846</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>45846</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>45342</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>46164</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>45139</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29172,7 +29172,7 @@
         <v>45537</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45843</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29318,7 +29318,7 @@
         <v>44739</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29391,7 +29391,7 @@
         <v>45104</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
         <v>45110</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>46168</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>45147</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>45856</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>45602</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29829,7 +29829,7 @@
         <v>45062</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>44753</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>45002</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>46171</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45078</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>45429</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45152</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>45581</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>46182</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30501,7 +30501,7 @@
         <v>44494</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30574,7 +30574,7 @@
         <v>46181</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30647,7 +30647,7 @@
         <v>45706</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>45104</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>46181</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>45460</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>46181</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31017,7 +31017,7 @@
         <v>46182</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>45653</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>45719</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>45115</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>46184</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45316</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>46184</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31533,7 +31533,7 @@
         <v>45545</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>45670</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>45588</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>45534</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31835,7 +31835,7 @@
         <v>45118</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>45600</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>46195</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>45610</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>45921</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>46198</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>45169</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>45747</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>46199</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>45169</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>45715</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>46202</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>46199</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>46202</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>45076</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>46205</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44606</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>44829</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>44762</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>44658</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>45646</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>44565</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>46209</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>46252</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>45691</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>46209</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>45201</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>44600</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33884,7 +33884,7 @@
         <v>46140</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>46253</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>46210</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>46210</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45440</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>45432</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45428</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>46168</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>46212</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>46212</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>45432</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>44586</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>46216</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>44753</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34911,7 +34911,7 @@
         <v>45237</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>44729</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>46259</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>46259</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35203,7 +35203,7 @@
         <v>45246</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>45702</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>45201</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35422,7 +35422,7 @@
         <v>46261</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>46261</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35568,7 +35568,7 @@
         <v>46218</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35641,7 +35641,7 @@
         <v>45724</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35714,7 +35714,7 @@
         <v>45251</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>46209</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44819</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>45195</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>46265</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>46265</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>44882</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>45169</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>45299</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>46265</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>46265</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45189</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>45460</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>46268</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>46267</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>45299</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>46268</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>46267</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45302</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>46229</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>46226</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>45099</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>46272</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37403,7 +37403,7 @@
         <v>46272</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>45310</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37549,7 +37549,7 @@
         <v>45503</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>44987</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>46276</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37768,7 +37768,7 @@
         <v>45201</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         <v>45071</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>45597</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37987,7 +37987,7 @@
         <v>46279</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>45128</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>45560</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>46279</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44848</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45432</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>44956</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>46281</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38586,7 +38586,7 @@
         <v>44987</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>44987</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38732,7 +38732,7 @@
         <v>45470</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38805,7 +38805,7 @@
         <v>45360</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>45225</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>45327</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39024,7 +39024,7 @@
         <v>45354</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45027</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>44980</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45280</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>44917</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39394,7 +39394,7 @@
         <v>45166</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>44651</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>44966</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>45001</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>44945</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>46287</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>46287</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>44992</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>45006</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>46287</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45201</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>45195</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>45402</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45139</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45775</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>46265</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>44617</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>44987</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>46042</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>46077</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40859,7 +40859,7 @@
         <v>46079</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>45272</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45062</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>45111</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>45545</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>46248</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>46247</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45363</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>45006</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>45082</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45012</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>45012</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>45246</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45057</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>45063</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>45104</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>45560</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>45105</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45001</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>44974</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42349,7 +42349,7 @@
         <v>45602</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42422,7 +42422,7 @@
         <v>44722</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42495,7 +42495,7 @@
         <v>45394</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42568,7 +42568,7 @@
         <v>44902</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42641,7 +42641,7 @@
         <v>45373</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>45359</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42787,7 +42787,7 @@
         <v>45360</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>44754</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>45072</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43006,7 +43006,7 @@
         <v>45053</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>45097</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>45462</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>44956</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>45058</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45327</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45402</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45775</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>45012</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45012</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>44756</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>45098</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45337</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45360</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45714</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>45001</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>45350</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>45350</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>45545</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>44774</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45169</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>45714</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45630</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45630</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45588</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44836,7 +44836,7 @@
         <v>44908</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44909,7 +44909,7 @@
         <v>45430</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44982,7 +44982,7 @@
         <v>45408</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45610</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>44973</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45278</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45019</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>45036</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>45119</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>45229</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>45600</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>45040</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>44950</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45043</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45685</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45357</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>44972</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45560</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45531</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>45394</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45104</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46384,7 +46384,7 @@
         <v>45574</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
         <v>45104</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45691</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>45608</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45502</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>44966</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45527</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45567</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45785</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45724</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>45551</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>45579</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45530</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45562</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>45527</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45646</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45280</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45546</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45791</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>44474</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47859,7 +47859,7 @@
         <v>44755</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>44608</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>44986</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>44483</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45485</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>45646</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>45602</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>45573</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45656</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>44959</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>45457</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45154</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         <v>45154</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>46050</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48891,7 +48891,7 @@
         <v>46064</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>46099</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -601,7 +601,7 @@
         <v>43955</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45791</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44789</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44931</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45153</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45103</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>45471</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45093</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>44630</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>44762</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45594</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44645</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>44762</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>46071</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>45973</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>46253</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>45230</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>44676</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45884</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>44655</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>44998</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>44888</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>45152</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>45588</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>46188</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>45741</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44039</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>44657</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>44756</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>44957</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>45545</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>46091</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44973</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>45012</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>46133</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>45357</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>45559</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>46175</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>46181</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>46182</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45063</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>46252</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>45194</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>44980</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45559</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>45717</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45457</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>45699</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>46139</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>44546</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>44825</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>44880</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44649</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44630</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>44860</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44880</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>44676</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>44510</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>44504</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>44848</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>44827</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44592</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44581</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44753</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44845</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44790</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44608</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>44693</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>44860</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44762</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>44825</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>44565</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>44503</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44490</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44474</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>44468</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44596</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>44576</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>44721</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>44762</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>44762</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44882</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44532</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44494</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>44806</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>44518</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>44501</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44845</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44872</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>44886</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>44630</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>44694</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44504</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>44853</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44817</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>44638</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44812</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44637</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44539</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44586</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>44713</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44762</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44494</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>44627</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>44630</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45719</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45621</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45196</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>44778</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>45360</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>45051</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>45536</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>45310</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>44893</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>45378</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>44806</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>45342</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>45342</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>45238</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>45426</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>45381</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>45754</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11603,7 +11603,7 @@
         <v>45086</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>45261</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>45121</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>44903</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
         <v>45505</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>45099</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>44884</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44817</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>44939</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>45328</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>44595</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44944</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>45012</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>44980</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45888</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>45757</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>45597</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>45672</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>45889</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>45888</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>45889</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>45892</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>44973</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>45194</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>45619</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>45303</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>45078</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45597</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>46048</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>45646</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>45426</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>46046</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>45807</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>45280</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>45589</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>46050</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>44992</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14339,7 +14339,7 @@
         <v>46052</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>45559</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45841</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>46052</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>45247</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45749</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>45743</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>45807</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45910</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>45843</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45910</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>44903</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>45387</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>45915</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>44627</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>45616</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>45178</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45915</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45915</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>45915</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>45602</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>45915</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         <v>45915</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>46059</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>46059</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>45918</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>45551</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>45918</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>45579</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>44489</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>46066</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         <v>44565</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>46069</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         <v>45803</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>45490</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>45923</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>46071</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>45104</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>46071</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>45505</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>46073</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>45192</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45194</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>46073</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45925</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45706</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>46078</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>46078</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         <v>46078</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>46079</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>46079</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>46079</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>46078</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>46078</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45932</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>45932</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>45197</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>45785</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45722</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45932</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>46086</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>46086</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>45588</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44944</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45937</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>45937</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45071</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45054</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45238</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45091</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44754</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45947</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>45950</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45739</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>46105</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>46104</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45559</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>46104</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>46104</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45951</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45068</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>45954</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45280</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>46104</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45085</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45009</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>45009</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>46112</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45012</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>44966</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45299</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>46119</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>45328</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>45328</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45009</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>46126</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>45480</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45328</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45813</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45974</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>45061</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44713</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>45978</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45975</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>45978</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>46133</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>45166</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>45981</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22333,7 +22333,7 @@
         <v>45001</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45811</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>45986</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
         <v>45986</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>45646</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22698,7 +22698,7 @@
         <v>45964</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>45178</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>45677</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>45932</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         <v>45757</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>45821</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         <v>45117</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         <v>45673</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45992</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45903</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>45929</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>45560</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>45440</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>45625</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>44992</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45954</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45670</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45889</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45855</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45889</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>44966</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45995</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>44822</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>46000</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>46140</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>46140</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>45891</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>45891</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>46139</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>44987</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>44739</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>46007</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>46007</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25132,7 +25132,7 @@
         <v>46062</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>45706</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>45482</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>45085</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>45193</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>45194</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>46140</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>45555</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>45413</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44748</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>45743</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>46139</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>46140</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>45754</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>44916</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45825</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>44862</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>45827</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>45827</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>45264</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>44917</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>45090</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>46147</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26831,7 +26831,7 @@
         <v>46149</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         <v>46149</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>44882</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44466</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>45266</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>44880</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45196</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>45600</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>45833</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>45838</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>45838</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>45835</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>45835</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>45436</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>44966</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27931,7 +27931,7 @@
         <v>45646</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>45303</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>45303</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>45840</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28223,7 +28223,7 @@
         <v>46162</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>45194</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>45841</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>45118</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>46162</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>46162</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>45341</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>45168</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>45846</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>45846</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>45342</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>46164</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>45139</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29172,7 +29172,7 @@
         <v>45537</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45843</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29318,7 +29318,7 @@
         <v>44739</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29391,7 +29391,7 @@
         <v>45104</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
         <v>45110</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>46168</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>45147</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>45856</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>45602</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29829,7 +29829,7 @@
         <v>45062</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>44753</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>45002</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>46171</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45078</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>45429</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45152</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>45581</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>46182</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30501,7 +30501,7 @@
         <v>44494</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30574,7 +30574,7 @@
         <v>46181</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30647,7 +30647,7 @@
         <v>45706</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>45104</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>46181</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>45460</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>46181</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31017,7 +31017,7 @@
         <v>46182</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>45653</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>45719</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>45115</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>46184</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45316</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>46184</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31533,7 +31533,7 @@
         <v>45545</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>45670</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>45588</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>45534</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31835,7 +31835,7 @@
         <v>45118</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>45600</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>46195</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>45610</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>45921</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>46198</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>45169</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>45747</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>46199</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>45169</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>45715</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32638,7 +32638,7 @@
         <v>46202</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>46199</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>46202</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>45076</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>46205</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44606</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>44829</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>44762</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>44658</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>45646</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>44565</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>46209</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>46252</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>45691</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>46209</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>45201</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>44600</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33884,7 +33884,7 @@
         <v>46140</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>46253</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>46210</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>46210</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45440</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>45432</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45428</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>46168</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>46212</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>46212</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>45432</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>44586</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>46216</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>44753</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34911,7 +34911,7 @@
         <v>45237</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>44729</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>46259</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>46259</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35203,7 +35203,7 @@
         <v>45246</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>45702</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>45201</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35422,7 +35422,7 @@
         <v>46261</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>46261</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35568,7 +35568,7 @@
         <v>46218</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35641,7 +35641,7 @@
         <v>45724</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35714,7 +35714,7 @@
         <v>45251</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>46209</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44819</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>45195</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>46265</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>46265</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>44882</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>45169</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>45299</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>46265</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>46265</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45189</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>45460</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>46268</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>46267</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>45299</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>46268</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>46267</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45302</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>46229</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>46226</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>45099</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>46272</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37403,7 +37403,7 @@
         <v>46272</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>45310</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37549,7 +37549,7 @@
         <v>45503</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>44987</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>46276</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37768,7 +37768,7 @@
         <v>45201</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         <v>45071</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>45597</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37987,7 +37987,7 @@
         <v>46279</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>45128</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>45560</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>46279</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44848</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45432</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>44956</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38513,7 +38513,7 @@
         <v>46281</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38586,7 +38586,7 @@
         <v>44987</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>44987</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38732,7 +38732,7 @@
         <v>45470</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38805,7 +38805,7 @@
         <v>45360</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>45225</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>45327</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39024,7 +39024,7 @@
         <v>45354</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45027</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>44980</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45280</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>44917</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39394,7 +39394,7 @@
         <v>45166</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>44651</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>44966</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>45001</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>44945</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>46287</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>46287</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>44992</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>45006</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>46287</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>45201</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>45195</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>45402</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45139</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45775</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>46265</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>44617</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>44987</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>46042</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>46077</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40859,7 +40859,7 @@
         <v>46079</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>45272</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45062</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41083,7 +41083,7 @@
         <v>45111</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>45545</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>46248</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>46247</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45363</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>45006</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>45082</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45012</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>45012</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>45246</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>45057</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>45063</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>45104</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>45560</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>45105</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45001</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>44974</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42349,7 +42349,7 @@
         <v>45602</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42422,7 +42422,7 @@
         <v>44722</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42495,7 +42495,7 @@
         <v>45394</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42568,7 +42568,7 @@
         <v>44902</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42641,7 +42641,7 @@
         <v>45373</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>45359</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42787,7 +42787,7 @@
         <v>45360</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>44754</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>45072</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43006,7 +43006,7 @@
         <v>45053</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>45097</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>45462</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>44956</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>45058</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45327</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45402</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45775</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>45012</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45012</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>44756</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>45098</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45337</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45360</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45714</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>45001</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>45350</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>45350</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>45545</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>44774</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45169</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>45714</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45630</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45630</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45588</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44836,7 +44836,7 @@
         <v>44908</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44909,7 +44909,7 @@
         <v>45430</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44982,7 +44982,7 @@
         <v>45408</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45610</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>44973</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45278</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>45019</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>45036</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>45119</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>45229</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>45600</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>45040</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>44950</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45043</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45685</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45357</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>44972</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45560</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45531</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>45394</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45104</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46384,7 +46384,7 @@
         <v>45574</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
         <v>45104</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45691</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>45608</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45502</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>44966</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45527</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45567</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45785</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45724</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>45551</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>45579</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45530</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45562</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>45527</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45646</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45280</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45546</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45791</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>44474</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47859,7 +47859,7 @@
         <v>44755</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>44608</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>44986</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>44483</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45485</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>45646</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>45602</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>45573</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45656</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>44959</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>45457</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45154</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         <v>45154</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>46050</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48891,7 +48891,7 @@
         <v>46064</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>46099</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -601,7 +601,7 @@
         <v>43955</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45791</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44789</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44931</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45153</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45093</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>45471</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45103</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>44630</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>44762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44645</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>44762</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>46071</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>45973</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>46253</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>45230</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>44676</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45884</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>44655</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>45588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>45741</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>46188</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44998</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44888</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>45152</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44039</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>44657</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>44756</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45699</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>45545</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>44957</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>46091</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>45357</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>46133</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>45194</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>44980</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>46175</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>46182</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45559</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>46252</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>44973</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>45717</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>45012</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45063</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>45559</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>45457</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>46139</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>44546</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>44825</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>44880</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44649</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44630</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>44860</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44880</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>44676</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>44504</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>44848</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>44827</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>44581</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44592</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44510</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44753</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44845</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44790</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44608</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>44860</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>44693</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44762</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>44825</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>44565</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>44503</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44490</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44474</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>44596</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44576</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>44721</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>44762</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>44762</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>44882</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44532</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44494</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44806</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>44518</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>44501</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>44845</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44872</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44886</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>44630</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>44694</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>44504</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>44853</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44638</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>44812</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44637</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44539</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44586</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44713</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>44762</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>44627</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44630</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45706</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>44494</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45432</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>44903</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45251</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>45602</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44903</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45328</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>45121</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>45012</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>45071</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>45261</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44987</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44617</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>45012</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45341</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45600</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>44987</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>45328</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45546</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45724</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>45747</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>45579</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>45588</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44944</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>45196</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>45530</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>45646</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>45562</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>45621</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>45551</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>45280</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45310</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45238</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>45600</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>44627</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>45551</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>46007</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>46007</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>45098</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45128</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>45363</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>45691</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45482</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>45739</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>44987</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>44987</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>44939</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>45888</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>45889</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>45670</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45888</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>45889</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>45892</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>45061</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>45432</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>45169</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>45201</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45201</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45115</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45807</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44908</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>45791</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>45841</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>45749</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>45743</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>45843</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>45807</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>45910</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>45910</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>45915</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>45915</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>45915</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>45915</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>45915</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45915</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45012</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>45672</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>46046</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44973</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45078</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>46048</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>45597</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>45194</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>45918</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>45247</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>46050</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>45579</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>45918</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>45490</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>45803</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>45147</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>45785</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>44880</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>46052</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>46052</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>45923</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>45925</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>45706</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>44822</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>45719</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>46059</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>46059</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>45426</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>45932</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>45932</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>45932</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>46066</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>46069</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>45937</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>46071</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>45440</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45937</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>46071</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>46073</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>46073</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45299</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>46078</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>46078</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>44754</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45169</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>44884</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>46078</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45947</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>46078</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>46078</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>45950</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>46079</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>46079</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>46079</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45951</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>45043</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>45954</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>45402</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>46086</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>46086</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>44600</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>45813</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45646</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45099</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45006</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>45719</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>45754</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45974</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45714</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>46104</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>46104</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>46104</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>45192</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>45975</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>45978</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>45225</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>46105</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45646</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>45978</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>45280</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>45981</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>46104</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>45360</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>45559</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>46112</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>45413</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45986</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45986</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>46119</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45992</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>45827</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>45743</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45460</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>45827</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>46126</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>45995</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>45855</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>45825</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>46000</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>45104</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>46133</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45833</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>45280</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>45280</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45835</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>45835</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45104</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>46062</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45111</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45625</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45838</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>45838</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>44848</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>45677</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44992</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>46139</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45840</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>44916</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>45811</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>45387</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45843</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>45560</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>45537</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>45505</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>45670</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>45932</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>45929</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         <v>45846</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         <v>45846</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>45891</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>45891</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>45673</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45266</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>45440</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>45616</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>45053</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>45429</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>46139</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>45597</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>45630</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>45630</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44944</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>45821</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
         <v>45964</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>45856</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>45019</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>45954</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>44722</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>44756</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>45085</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>45889</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26967,7 +26967,7 @@
         <v>45012</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>45462</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27113,7 +27113,7 @@
         <v>45903</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27186,7 +27186,7 @@
         <v>45889</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27259,7 +27259,7 @@
         <v>44966</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>44966</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27405,7 +27405,7 @@
         <v>45272</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>45299</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27551,7 +27551,7 @@
         <v>46140</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>45432</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>46140</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>44966</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27843,7 +27843,7 @@
         <v>45001</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27916,7 +27916,7 @@
         <v>45001</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>46140</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>45505</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>46140</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>45359</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>45090</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>45589</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>45194</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>44917</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>45168</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28651,7 +28651,7 @@
         <v>45706</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>45071</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28797,7 +28797,7 @@
         <v>45597</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>45197</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
         <v>45099</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>45360</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>44565</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>44980</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44586</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29313,7 +29313,7 @@
         <v>46147</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>45610</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29459,7 +29459,7 @@
         <v>46149</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29532,7 +29532,7 @@
         <v>44595</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>46149</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29678,7 +29678,7 @@
         <v>44754</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>44753</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>45166</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>45001</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>45646</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>45002</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>45460</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>45653</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>45246</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30335,7 +30335,7 @@
         <v>45299</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30408,7 +30408,7 @@
         <v>45001</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>45036</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>45357</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30632,7 +30632,7 @@
         <v>45054</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>45841</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30778,7 +30778,7 @@
         <v>45555</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>45394</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>45581</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30997,7 +30997,7 @@
         <v>45402</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31070,7 +31070,7 @@
         <v>45381</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>45646</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31216,7 +31216,7 @@
         <v>45169</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         <v>45354</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>46162</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         <v>45009</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>45009</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>46162</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>46162</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>45702</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>46164</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>44739</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>46168</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45588</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>46171</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>45278</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>45602</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>45754</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>44987</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45715</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>45117</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>45480</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45302</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45327</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45757</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>44729</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>46182</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>46181</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>46181</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33202,7 +33202,7 @@
         <v>46182</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>46181</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33353,7 +33353,7 @@
         <v>45619</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>46184</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>46184</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>45714</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>45337</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33718,7 +33718,7 @@
         <v>44917</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>44778</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>44494</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>44973</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>44966</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>44489</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>44762</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>46199</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>45921</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44739</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>44753</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>46198</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>44862</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>45470</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>46199</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>46202</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>45086</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>45310</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>45040</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>46202</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>45757</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>44829</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>44956</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35407,7 +35407,7 @@
         <v>45166</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>44882</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45534</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>46205</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>44893</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>45610</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>46210</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>46209</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>46210</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>44972</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>44882</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>46209</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45009</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>46168</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>46212</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>46212</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>46140</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45062</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>46216</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36799,7 +36799,7 @@
         <v>45316</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>45342</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36945,7 +36945,7 @@
         <v>44713</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>46209</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>46218</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>46259</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37237,7 +37237,7 @@
         <v>46259</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>46261</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>46261</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>45426</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37529,7 +37529,7 @@
         <v>46265</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>45588</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45194</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>46265</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>44817</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45559</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>46265</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>45328</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45328</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45360</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>45360</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>46265</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>45104</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>45775</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>45105</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>44945</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>46268</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>44606</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38858,7 +38858,7 @@
         <v>46267</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         <v>46226</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>46268</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39077,7 +39077,7 @@
         <v>46267</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>45178</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>45068</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45536</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>46272</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>46272</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>46229</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>45072</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>46279</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>46279</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>46276</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>46281</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45196</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45195</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>45082</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         <v>45193</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>45264</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45085</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45091</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>46287</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>46287</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>45110</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>45152</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>46287</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45139</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>45169</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45118</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>45178</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>45062</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41224,7 +41224,7 @@
         <v>45201</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45195</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41370,7 +41370,7 @@
         <v>45027</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>45602</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>45378</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>45436</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>46247</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>45350</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41813,7 +41813,7 @@
         <v>45350</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>45303</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41959,7 +41959,7 @@
         <v>45303</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>46265</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>46077</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>44974</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>46292</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
         <v>44806</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>46248</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>46292</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>44992</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>46079</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>45246</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>44565</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>45775</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>46042</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>45237</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>44774</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>45545</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>45303</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>46253</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>46294</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43434,7 +43434,7 @@
         <v>45430</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>44956</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43580,7 +43580,7 @@
         <v>45342</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45342</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>45428</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>46252</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>45373</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>45724</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44018,7 +44018,7 @@
         <v>44651</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45560</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>45408</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45097</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>45189</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45051</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45006</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>45118</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44607,7 +44607,7 @@
         <v>45139</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44680,7 +44680,7 @@
         <v>45076</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>44819</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44826,7 +44826,7 @@
         <v>44658</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>45685</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45545</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>45119</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>45201</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45191,7 +45191,7 @@
         <v>44992</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45063</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45347,7 +45347,7 @@
         <v>44748</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45078</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>45327</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45600</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45639,7 +45639,7 @@
         <v>44980</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>44950</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45722</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45058</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45560</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>45194</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45057</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45012</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>45012</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>44902</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45238</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45545</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45229</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46603,7 +46603,7 @@
         <v>45104</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45104</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46759,7 +46759,7 @@
         <v>45574</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>45527</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46905,7 +46905,7 @@
         <v>45531</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45560</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45691</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>45394</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>45608</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>44966</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45104</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>45502</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45785</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>45567</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>45527</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>44474</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>44755</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>44608</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>44986</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>44483</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>45485</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>45646</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48234,7 +48234,7 @@
         <v>45602</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>45573</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48380,7 +48380,7 @@
         <v>45656</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48453,7 +48453,7 @@
         <v>44959</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>45457</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45154</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45154</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>46050</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>46064</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>46099</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -601,7 +601,7 @@
         <v>43955</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45791</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44789</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44931</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45153</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45093</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>45471</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45103</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>44630</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>44762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44645</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>44762</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>46071</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>45973</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>46253</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>45230</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>44676</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45884</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>44655</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>45588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>45741</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>46188</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44998</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44888</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>45152</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44039</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>44657</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>44756</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45699</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>45545</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>44957</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>46091</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>45357</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>46133</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>45194</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>44980</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>46175</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>46182</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45559</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>46252</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>44973</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>45717</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>45012</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45063</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>45559</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>45457</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>46139</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>44546</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>44825</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>44880</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44649</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44630</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>44860</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44880</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>44676</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>44504</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>44848</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>44827</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>44581</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44592</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44510</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44753</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44845</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44790</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44608</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>44860</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>44693</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44762</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>44825</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>44565</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>44503</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44490</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44474</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>44596</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44576</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>44721</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>44762</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>44762</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>44882</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44532</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44494</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44806</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>44518</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>44501</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>44845</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44872</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44886</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>44630</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>44694</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>44504</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>44853</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44638</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>44812</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44637</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44539</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44586</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44713</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>44762</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>44627</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44630</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45706</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>44494</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45432</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>44903</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45251</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>45602</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44903</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45328</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>45121</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>45012</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>45071</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>45261</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44987</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44617</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>45012</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45341</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45600</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>44987</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>45328</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>45546</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45724</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>45747</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>45579</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>45588</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44944</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>45196</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>45530</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>45646</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>45562</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>45621</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>45551</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>45280</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45310</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45238</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>45600</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>44627</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>45551</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>46007</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>46007</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>45098</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45128</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>45363</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>45691</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45482</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>45739</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>44987</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>44987</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>44939</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>45888</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>45889</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>45670</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45888</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>45889</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>45892</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>45061</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>45432</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>45169</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>45201</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45201</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45115</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45807</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44908</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>45791</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>45841</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>45749</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>45743</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>45843</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>45807</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>45910</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>45910</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>45915</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>45915</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>45915</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>45915</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>45915</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45915</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45012</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>45672</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>46046</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44973</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45078</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>46048</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>45597</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>45194</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>45918</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>45247</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>46050</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>45579</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>45918</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>45490</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>45803</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>45147</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>45785</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>44880</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>46052</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>46052</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>45923</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>45925</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>45706</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>44822</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>45719</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>46059</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>46059</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>45426</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>45932</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>45932</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>45932</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>46066</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>46069</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>45937</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>46071</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>45440</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45937</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>46071</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>46073</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>46073</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45299</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>46078</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>46078</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>44754</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45169</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>44884</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>46078</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45947</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>46078</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>46078</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>45950</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>46079</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>46079</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>46079</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45951</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>45043</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>45954</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>45402</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>46086</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>46086</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>44600</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>45813</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45646</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45099</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45006</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>45719</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>45754</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45974</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45714</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>46104</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>46104</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>46104</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>45192</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>45975</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>45978</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>45225</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>46105</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45646</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>45978</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>45280</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>45981</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>46104</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>45360</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>45559</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>46112</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>45413</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45986</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45986</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>46119</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45992</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>45827</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>45743</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45460</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>45827</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>46126</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>45995</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>45855</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>45825</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>46000</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>45104</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>46133</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45833</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>45280</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>45280</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45835</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>45835</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45104</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>46062</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45111</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45625</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45838</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>45838</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>44848</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>45677</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44992</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>46139</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>45840</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>44916</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>45811</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24596,7 +24596,7 @@
         <v>45387</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         <v>45843</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>45560</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>45537</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>45505</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>45670</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>45932</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>45929</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         <v>45846</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         <v>45846</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>45891</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>45891</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>45673</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45266</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>45440</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25711,7 +25711,7 @@
         <v>45616</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>45053</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>45429</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>46139</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>45597</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>45630</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>45630</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>44944</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>45821</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
         <v>45964</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>45856</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>45019</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>45954</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>44722</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>44756</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>45085</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>45889</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26967,7 +26967,7 @@
         <v>45012</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>45462</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27113,7 +27113,7 @@
         <v>45903</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27186,7 +27186,7 @@
         <v>45889</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27259,7 +27259,7 @@
         <v>44966</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>44966</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27405,7 +27405,7 @@
         <v>45272</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>45299</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27551,7 +27551,7 @@
         <v>46140</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>45432</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>46140</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>44966</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27843,7 +27843,7 @@
         <v>45001</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27916,7 +27916,7 @@
         <v>45001</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>46140</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>45505</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>46140</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>45359</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>45090</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>45589</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>45194</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>44917</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>45168</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28651,7 +28651,7 @@
         <v>45706</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>45071</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28797,7 +28797,7 @@
         <v>45597</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>45197</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
         <v>45099</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>45360</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>44565</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>44980</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44586</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29313,7 +29313,7 @@
         <v>46147</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>45610</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29459,7 +29459,7 @@
         <v>46149</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29532,7 +29532,7 @@
         <v>44595</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>46149</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29678,7 +29678,7 @@
         <v>44754</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>44753</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>45166</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>45001</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>45646</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>45002</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>45460</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>45653</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>45246</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30335,7 +30335,7 @@
         <v>45299</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30408,7 +30408,7 @@
         <v>45001</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>45036</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>45357</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30632,7 +30632,7 @@
         <v>45054</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>45841</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30778,7 +30778,7 @@
         <v>45555</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>45394</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>45581</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30997,7 +30997,7 @@
         <v>45402</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31070,7 +31070,7 @@
         <v>45381</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>45646</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31216,7 +31216,7 @@
         <v>45169</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         <v>45354</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>46162</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         <v>45009</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>45009</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>46162</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>46162</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>45702</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>46164</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>44739</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>46168</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45588</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>46171</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>45278</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>45602</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>45754</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>44987</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45715</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>45117</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>45480</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45302</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45327</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45757</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>44729</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>46182</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>46181</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>46181</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33202,7 +33202,7 @@
         <v>46182</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>46181</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33353,7 +33353,7 @@
         <v>45619</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>46184</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>46184</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>45714</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33645,7 +33645,7 @@
         <v>45337</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33718,7 +33718,7 @@
         <v>44917</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>44778</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>44494</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>44973</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>44966</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>44489</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>44762</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>46199</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>45921</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44739</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>44753</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>46198</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>44862</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>45470</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>46199</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>46202</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>45086</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>45310</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>45040</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>46202</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>45757</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>44829</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>44956</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35407,7 +35407,7 @@
         <v>45166</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>44882</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45534</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>46205</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>44893</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>45610</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>46210</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>46209</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>46210</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>44972</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>44882</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>46209</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45009</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>46168</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>46212</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>46212</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>46140</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45062</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>46216</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36799,7 +36799,7 @@
         <v>45316</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>45342</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36945,7 +36945,7 @@
         <v>44713</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>46209</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>46218</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>46259</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37237,7 +37237,7 @@
         <v>46259</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>46261</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>46261</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>45426</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37529,7 +37529,7 @@
         <v>46265</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>45588</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45194</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>46265</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>44817</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45559</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>46265</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>45328</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45328</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45360</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>45360</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>46265</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>45104</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>45775</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>45105</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>44945</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>46268</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>44606</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38858,7 +38858,7 @@
         <v>46267</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         <v>46226</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>46268</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39077,7 +39077,7 @@
         <v>46267</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>45178</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>45068</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45536</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>46272</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>46272</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>46229</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>45072</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>46279</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>46279</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>46276</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>46281</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45196</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45195</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>45082</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         <v>45193</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>45264</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45085</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45091</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>46287</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>46287</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>45110</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>45152</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>46287</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45139</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>45169</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>45118</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>45178</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41146,7 +41146,7 @@
         <v>45062</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41224,7 +41224,7 @@
         <v>45201</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45195</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41370,7 +41370,7 @@
         <v>45027</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>45602</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>45378</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>45436</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>46247</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>45350</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41813,7 +41813,7 @@
         <v>45350</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>45303</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41959,7 +41959,7 @@
         <v>45303</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>46265</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>46077</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>44974</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>46292</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
         <v>44806</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>46248</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>46292</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>44992</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>46079</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>45246</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>44565</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>45775</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>46042</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>45237</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>44774</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>45545</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>45303</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>46253</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>46294</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43434,7 +43434,7 @@
         <v>45430</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>44956</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43580,7 +43580,7 @@
         <v>45342</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45342</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>45428</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>46252</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>45373</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>45724</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44018,7 +44018,7 @@
         <v>44651</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45560</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>45408</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45097</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>45189</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45051</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45006</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>45118</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44607,7 +44607,7 @@
         <v>45139</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44680,7 +44680,7 @@
         <v>45076</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>44819</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44826,7 +44826,7 @@
         <v>44658</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>45685</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45545</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>45119</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>45201</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45191,7 +45191,7 @@
         <v>44992</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45063</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45347,7 +45347,7 @@
         <v>44748</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45078</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>45327</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45600</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45639,7 +45639,7 @@
         <v>44980</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>44950</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45722</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45058</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>45560</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>45194</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45057</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45012</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>45012</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>44902</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45238</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45545</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45229</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46603,7 +46603,7 @@
         <v>45104</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45104</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46759,7 +46759,7 @@
         <v>45574</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>45527</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46905,7 +46905,7 @@
         <v>45531</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45560</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45691</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>45394</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>45608</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>44966</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45104</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>45502</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45785</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>45567</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>45527</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>44474</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>44755</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>44608</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>44986</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>44483</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>45485</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>45646</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48234,7 +48234,7 @@
         <v>45602</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>45573</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48380,7 +48380,7 @@
         <v>45656</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48453,7 +48453,7 @@
         <v>44959</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>45457</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45154</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45154</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>46050</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>46064</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>46099</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -601,7 +601,7 @@
         <v>43955</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45791</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44789</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44931</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45153</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45103</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>45093</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45471</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>44630</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>44762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44645</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>44762</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>46071</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>45973</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>46253</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>45230</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>44676</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44888</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45152</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>45588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>45884</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>45741</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44655</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44998</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>46188</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44039</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>44657</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>44756</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45559</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44957</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>45717</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>45559</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>45063</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>45457</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>45699</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>45545</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>44973</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>45194</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>45012</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>45357</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>44980</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>46133</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46091</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>46175</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>46181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>46182</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>46252</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>46139</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>44546</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>44825</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>44649</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44880</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44860</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>44880</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44676</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>44630</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>44510</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>44504</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>44848</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>44827</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44581</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44592</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44753</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44845</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44790</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44693</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>44608</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>44860</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44762</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>44825</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>44565</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>44503</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44490</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44596</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>44853</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44817</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>44637</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>44638</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>44494</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>44576</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>44721</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>44518</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>44806</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>44501</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>44845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>44539</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>44586</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>44713</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>44872</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>44886</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>44630</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>44812</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>44762</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>44762</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>44882</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44532</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44694</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44762</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>45090</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>44504</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>44494</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>45342</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45342</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>44754</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45072</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45310</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>44893</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>45378</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>44627</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>44806</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>44630</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>44882</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>45053</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>45097</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>45266</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>45621</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44880</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45196</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45051</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45462</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>45600</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>44956</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45719</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>45058</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>45436</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>45327</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>45402</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>45196</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44778</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>45360</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>45238</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>45426</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44966</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>45303</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>45303</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>45012</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>45012</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>45381</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>44756</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>45754</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45194</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>45341</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>45168</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>45536</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>45086</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>45342</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>45098</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>45139</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>45337</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>45104</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>45261</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>45360</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>45110</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>45121</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>45147</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>45505</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>44903</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45099</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>45714</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>44939</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>44884</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>45001</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>45602</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>44817</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>45350</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45350</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>45545</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>44774</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>45169</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45888</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>45062</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44753</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>45757</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>45714</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>45328</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>45002</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>45630</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>45630</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>45588</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>44908</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>45430</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44595</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>45889</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>45078</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45408</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>45610</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>44944</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>45429</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>44973</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>45888</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>45889</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45892</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>45012</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>45278</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>45019</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44980</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45036</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>45119</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>45229</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>45600</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45807</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>45040</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44950</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45619</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45152</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>45303</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>45043</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>45581</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>45841</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>45685</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45357</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>44972</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>45597</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45646</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>44494</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>45560</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>45531</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>45749</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45743</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45807</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>45394</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>45104</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45910</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>45574</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>45843</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45104</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>45691</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>45910</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>45426</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45608</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45502</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>44966</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45527</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>45706</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45280</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>45104</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>45589</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>45460</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44992</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>45915</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>45559</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45719</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45567</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45915</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>45915</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45115</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45915</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>45915</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45915</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>45316</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>44903</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>45785</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>45387</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>45724</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45551</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>45579</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>45530</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
         <v>45918</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>44627</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21787,7 +21787,7 @@
         <v>45918</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>45616</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>45178</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>45602</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>45545</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45562</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45527</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45670</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45588</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>45551</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>45646</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22605,7 +22605,7 @@
         <v>44489</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>45280</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>45534</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>45546</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44565</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>45118</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>45600</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>45923</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>45104</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>45505</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>45791</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>45925</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45706</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>45192</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45194</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>45610</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45169</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45747</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45169</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>45197</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>45932</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>45722</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>45932</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45932</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>45588</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44944</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24538,7 +24538,7 @@
         <v>45597</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>45672</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>45076</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>44973</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>45194</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45071</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>45078</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>45247</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>45054</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>45579</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>45803</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>45238</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>44606</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         <v>44829</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>45490</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44762</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>45091</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44658</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>45646</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>45937</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44754</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>45785</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>44565</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45739</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>45691</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>45559</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>45201</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44600</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>45068</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>45440</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>45432</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>45428</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>45813</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26967,7 +26967,7 @@
         <v>45280</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>45085</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27113,7 +27113,7 @@
         <v>45432</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27186,7 +27186,7 @@
         <v>45947</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27259,7 +27259,7 @@
         <v>45009</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>45009</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27405,7 +27405,7 @@
         <v>45950</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>45012</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>44966</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>45299</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>45328</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>45328</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>45413</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>44586</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27994,7 +27994,7 @@
         <v>45009</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28067,7 +28067,7 @@
         <v>45825</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>45951</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>45480</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>45827</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>45827</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>45328</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>44753</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>45237</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>44729</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>45954</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>45061</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>45246</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>44713</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>45702</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>45201</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29172,7 +29172,7 @@
         <v>45833</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45838</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29318,7 +29318,7 @@
         <v>45838</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29391,7 +29391,7 @@
         <v>45835</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
         <v>45835</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>45724</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>45251</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>44819</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>45166</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>45195</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>45840</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>45001</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>45646</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>45178</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44882</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>45846</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45757</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>45846</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30491,7 +30491,7 @@
         <v>45169</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>45117</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30637,7 +30637,7 @@
         <v>45299</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45537</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45843</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>45974</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>45189</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45460</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>45978</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>45975</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>45856</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44822</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>45299</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>45302</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>45978</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>45099</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>45653</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>44987</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>45310</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>44739</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31951,7 +31951,7 @@
         <v>45482</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>44987</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>45981</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>45085</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45193</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45194</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45555</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>45715</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>44748</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>45743</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45201</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45071</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45597</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45128</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>45986</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>45986</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>45560</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33202,7 +33202,7 @@
         <v>45754</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44848</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>44916</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>45432</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44956</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>46105</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>46104</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>46104</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>46104</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>44987</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>44987</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>44862</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45470</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>45360</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>45225</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>45327</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45354</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>46104</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>45027</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45264</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34667,7 +34667,7 @@
         <v>44980</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>45992</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34818,7 +34818,7 @@
         <v>45280</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>44917</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>45166</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>44917</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>44651</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>46119</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>44966</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>45855</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>45995</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>46126</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>45001</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>44945</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>46133</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>44992</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>45006</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45811</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>45201</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>45195</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>45964</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>45677</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45402</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45139</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45932</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>44617</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>45821</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>44987</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>46007</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36799,7 +36799,7 @@
         <v>46007</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>45673</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36945,7 +36945,7 @@
         <v>45903</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>45929</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45560</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37169,7 +37169,7 @@
         <v>45440</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>45625</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>44992</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37393,7 +37393,7 @@
         <v>45272</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37466,7 +37466,7 @@
         <v>45954</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>45670</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37612,7 +37612,7 @@
         <v>45062</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>45111</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>45889</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         <v>45545</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>45889</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37987,7 +37987,7 @@
         <v>44966</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>45363</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38133,7 +38133,7 @@
         <v>45006</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38206,7 +38206,7 @@
         <v>45082</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38284,7 +38284,7 @@
         <v>46140</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38357,7 +38357,7 @@
         <v>45012</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45012</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>45246</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>46140</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>45891</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38722,7 +38722,7 @@
         <v>45891</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>45057</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>46139</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45063</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>46062</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>45104</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>45706</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>45560</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45105</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39394,7 +39394,7 @@
         <v>45001</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>44974</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>46140</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>45602</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>46139</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>46140</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>46048</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>44722</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>45394</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>46046</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>44902</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>45373</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>45359</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45360</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>46050</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>46052</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>46052</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>46059</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>46059</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>46066</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>46147</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>46149</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>46149</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>46071</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>46073</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>46073</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>46078</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>46078</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>46078</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>46079</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>46078</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>46078</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>46086</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41818,7 +41818,7 @@
         <v>46086</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>45646</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>46162</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45841</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>46162</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>46162</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>46164</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>44739</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
         <v>46168</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>46171</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>46182</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>46181</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>46181</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>46182</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>46184</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>46184</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43006,7 +43006,7 @@
         <v>45921</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>46198</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>46199</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>46202</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>46199</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>46202</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>46209</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>46209</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>46140</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>46210</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>46210</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>46168</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>46212</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>46212</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>46216</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>46218</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>46209</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>46265</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>46265</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>46265</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>46265</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>46268</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>46267</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>46268</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>46267</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>46226</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>46272</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>46272</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>46276</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>46279</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>46279</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>46281</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>46287</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>46287</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>46287</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>45775</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>46042</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>46077</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>46079</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>46247</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>46294</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46024,7 +46024,7 @@
         <v>46248</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>46292</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46170,7 +46170,7 @@
         <v>46292</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46243,7 +46243,7 @@
         <v>46253</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46321,7 +46321,7 @@
         <v>46252</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>46300</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46467,7 +46467,7 @@
         <v>46300</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46540,7 +46540,7 @@
         <v>46300</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>45118</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46686,7 +46686,7 @@
         <v>46298</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46759,7 +46759,7 @@
         <v>46259</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>46259</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46905,7 +46905,7 @@
         <v>46302</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>46265</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>46261</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>46261</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>45775</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>46181</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>46112</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>44474</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>44755</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>44608</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>44986</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>44483</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45485</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47859,7 +47859,7 @@
         <v>45646</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>45602</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>45573</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48078,7 +48078,7 @@
         <v>45656</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>44959</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>45457</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>45154</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>45154</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>46050</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>46064</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>46099</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -601,7 +601,7 @@
         <v>43955</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45791</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44789</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44931</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45153</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45103</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>45093</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45471</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>44630</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>44762</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44645</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>44762</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>46071</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>45973</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>46253</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>45230</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>44676</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44888</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45152</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>45588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>45884</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>45741</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>44655</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44998</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>46188</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44039</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>44657</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>44756</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45559</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44957</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>45717</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>45559</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>45063</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>45457</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>45699</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>45545</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>44973</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>45194</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>45012</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>45357</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>44980</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>46133</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46091</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>46175</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>46181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>46182</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>46252</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>46139</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>44546</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>44825</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>44649</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44880</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44860</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>44880</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44676</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>44630</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>44510</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>44504</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>44848</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>44827</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44581</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44592</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44753</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44845</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44790</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44693</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>44608</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>44860</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44762</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>44825</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>44565</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>44503</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44490</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44596</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>44853</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44817</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>44637</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>44638</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>44494</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         <v>44576</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>44721</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>44518</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>44806</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>44501</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>44845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>44539</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>44586</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>44713</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>44872</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>44886</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>44630</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>44812</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>44762</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>44762</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>44882</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44532</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44694</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44762</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>45090</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>44504</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>44494</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>45342</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45342</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>44754</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>45072</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45310</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>44893</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>45378</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>44627</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>44806</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>44630</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>44882</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>45053</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>45097</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>45266</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>45621</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44880</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45196</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45051</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45462</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>45600</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>44956</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45719</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>45058</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>45436</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>45327</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>45402</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>45196</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44778</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>45360</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>45238</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>45426</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44966</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>45303</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>45303</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>45012</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>45012</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>45381</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>44756</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>45754</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45194</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>45341</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>45168</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>45536</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>45086</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>45342</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>45098</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>45139</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>45337</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>45104</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>45261</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>45360</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>45110</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>45121</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>45147</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>45505</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>44903</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45099</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>45714</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>44939</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         <v>44884</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>45001</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>45602</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>44817</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>45350</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45350</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>45545</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>44774</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>45169</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45888</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>45062</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44753</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>45757</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>45714</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>45328</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>45002</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>45630</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>45630</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>45588</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>44908</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>45430</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44595</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>45889</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>45078</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45408</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>45610</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>44944</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>45429</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>44973</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>45888</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>45889</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45892</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>45012</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>45278</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>45019</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44980</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45036</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>45119</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>45229</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>45600</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45807</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>45040</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44950</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45619</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45152</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>45303</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>45043</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>45581</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>45841</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>45685</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45357</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>44972</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>45597</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45646</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>44494</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>45560</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>45531</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>45749</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45743</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45807</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>45394</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>45104</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45910</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>45574</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>45843</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45104</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>45691</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>45910</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>45426</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45608</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45502</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>44966</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45527</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>45706</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45280</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>45104</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>45589</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>45460</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44992</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>45915</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>45559</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>45719</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45567</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45915</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>45915</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45115</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45915</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>45915</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45915</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>45316</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>44903</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>45785</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>45387</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>45724</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45551</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>45579</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21568,7 +21568,7 @@
         <v>45530</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
         <v>45918</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>44627</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21787,7 +21787,7 @@
         <v>45918</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>45616</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>45178</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>45602</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>45545</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45562</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45527</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45670</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45588</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>45551</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>45646</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22605,7 +22605,7 @@
         <v>44489</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>45280</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>45534</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>45546</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44565</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>45118</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>45600</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>45923</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>45104</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>45505</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>45791</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>45925</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45706</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>45192</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45194</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         <v>45610</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         <v>45169</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>45747</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>45169</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>45197</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>45932</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>45722</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>45932</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45932</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>45588</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44944</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24538,7 +24538,7 @@
         <v>45597</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>45672</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>45076</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>44973</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>45194</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45071</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>45078</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>45247</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>45054</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>45579</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>45803</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>45238</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>44606</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         <v>44829</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>45490</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44762</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>45091</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>44658</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>45646</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>45937</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>44754</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>45785</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>44565</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45739</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>45691</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>45559</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>45201</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>44600</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>45068</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>45440</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>45432</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>45428</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>45813</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26967,7 +26967,7 @@
         <v>45280</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>45085</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27113,7 +27113,7 @@
         <v>45432</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27186,7 +27186,7 @@
         <v>45947</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27259,7 +27259,7 @@
         <v>45009</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>45009</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27405,7 +27405,7 @@
         <v>45950</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>45012</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>44966</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>45299</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>45328</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>45328</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>45413</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>44586</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27994,7 +27994,7 @@
         <v>45009</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28067,7 +28067,7 @@
         <v>45825</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>45951</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>45480</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>45827</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>45827</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>45328</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>44753</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>45237</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>44729</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>45954</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>45061</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>45246</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28953,7 +28953,7 @@
         <v>44713</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>45702</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
         <v>45201</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29172,7 +29172,7 @@
         <v>45833</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>45838</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29318,7 +29318,7 @@
         <v>45838</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29391,7 +29391,7 @@
         <v>45835</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
         <v>45835</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>45724</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>45251</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
         <v>44819</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>45166</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>45195</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>45840</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29980,7 +29980,7 @@
         <v>45001</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>45646</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>45178</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44882</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>45846</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45757</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>45846</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30491,7 +30491,7 @@
         <v>45169</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>45117</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30637,7 +30637,7 @@
         <v>45299</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>45537</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45843</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>45974</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>45189</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45460</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>45978</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>45975</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>45856</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44822</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>45299</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>45302</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>45978</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>45099</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>45653</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>44987</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>45310</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>44739</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31951,7 +31951,7 @@
         <v>45482</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>44987</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>45981</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>45085</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45193</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45194</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45555</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>45715</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>44748</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>45743</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45201</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45071</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45597</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45128</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>45986</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>45986</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>45560</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33202,7 +33202,7 @@
         <v>45754</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44848</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>44916</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>45432</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>44956</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>46105</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>46104</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>46104</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>46104</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>44987</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>44987</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>44862</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45470</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>45360</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>45225</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>45327</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45354</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>46104</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>45027</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45264</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34667,7 +34667,7 @@
         <v>44980</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>45992</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34818,7 +34818,7 @@
         <v>45280</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>44917</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>45166</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>44917</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>44651</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>46119</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>44966</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>45855</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>45995</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>46126</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>45001</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>44945</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>46133</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>44992</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>45006</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45811</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>45201</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>45195</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>45964</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>45677</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45402</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45139</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45932</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>44617</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>45821</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>44987</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>46007</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36799,7 +36799,7 @@
         <v>46007</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>45673</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36945,7 +36945,7 @@
         <v>45903</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>45929</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45560</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37169,7 +37169,7 @@
         <v>45440</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>45625</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>44992</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37393,7 +37393,7 @@
         <v>45272</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37466,7 +37466,7 @@
         <v>45954</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>45670</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37612,7 +37612,7 @@
         <v>45062</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>45111</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>45889</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         <v>45545</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>45889</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37987,7 +37987,7 @@
         <v>44966</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>45363</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38133,7 +38133,7 @@
         <v>45006</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38206,7 +38206,7 @@
         <v>45082</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38284,7 +38284,7 @@
         <v>46140</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38357,7 +38357,7 @@
         <v>45012</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>45012</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>45246</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>46140</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>45891</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38722,7 +38722,7 @@
         <v>45891</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>45057</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>46139</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45063</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>46062</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>45104</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>45706</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>45560</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>45105</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39394,7 +39394,7 @@
         <v>45001</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>44974</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>46140</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>45602</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>46139</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>46140</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39832,7 +39832,7 @@
         <v>46048</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>44722</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>45394</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40051,7 +40051,7 @@
         <v>46046</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40124,7 +40124,7 @@
         <v>44902</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40197,7 +40197,7 @@
         <v>45373</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>45359</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45360</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>46050</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>46052</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>46052</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>46059</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>46059</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>46066</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>46147</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>46149</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>46149</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>46071</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>46073</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>46073</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>46078</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>46078</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>46078</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>46079</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>46078</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>46078</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>46086</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41818,7 +41818,7 @@
         <v>46086</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>45646</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>46162</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45841</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>46162</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>46162</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>46164</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>44739</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
         <v>46168</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>46171</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>46182</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>46181</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>46181</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>46182</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>46184</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>46184</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43006,7 +43006,7 @@
         <v>45921</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>46198</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>46199</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>46202</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>46199</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>46202</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>46209</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>46209</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>46140</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>46210</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>46210</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>46168</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>46212</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>46212</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>46216</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>46218</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>46209</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>46265</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>46265</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>46265</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>46265</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>46268</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>46267</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>46268</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>46267</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>46226</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>46272</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>46272</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>46276</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>46279</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>46279</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>46281</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>46287</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>46287</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>46287</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>45775</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>46042</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>46077</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>46079</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>46247</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>46294</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46024,7 +46024,7 @@
         <v>46248</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>46292</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46170,7 +46170,7 @@
         <v>46292</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46243,7 +46243,7 @@
         <v>46253</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46321,7 +46321,7 @@
         <v>46252</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>46300</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46467,7 +46467,7 @@
         <v>46300</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46540,7 +46540,7 @@
         <v>46300</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>45118</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46686,7 +46686,7 @@
         <v>46298</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46759,7 +46759,7 @@
         <v>46259</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>46259</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46905,7 +46905,7 @@
         <v>46302</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>46265</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>46261</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>46261</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>45775</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>46181</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>46112</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>44474</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>44755</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>44608</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>44986</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>44483</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45485</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47859,7 +47859,7 @@
         <v>45646</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>45602</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>45573</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48078,7 +48078,7 @@
         <v>45656</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>44959</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>45457</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>45154</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>45154</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>46050</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>46064</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>46099</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -601,7 +601,7 @@
         <v>43955</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45791</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44789</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44931</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45153</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45093</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>45471</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45103</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>44630</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>44762</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45594</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44645</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>44762</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>45973</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>46071</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>46253</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>45230</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>44676</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44655</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>45884</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>45588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>45741</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>46188</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44998</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44888</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>45152</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44039</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>44657</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>44756</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>44957</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>45357</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>45194</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44980</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>46175</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>46182</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>46181</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>46091</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>45559</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>46133</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>44973</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45717</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45012</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>45063</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>45559</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>46252</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>45457</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45699</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>45545</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>46139</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>44546</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>44825</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>44649</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44880</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44630</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>44860</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44880</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>44676</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>44510</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>44504</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>44848</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>44827</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44581</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44592</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44753</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44845</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44790</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44608</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>44693</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>44860</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44762</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>44825</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>44565</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>44503</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44490</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44596</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>44576</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44721</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>44762</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44762</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>44882</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>44532</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44494</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44518</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44806</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>44501</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>44845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>44872</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44630</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44886</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>44694</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>44504</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>44817</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44853</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>44638</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44812</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>44637</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44539</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44713</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44586</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44762</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>44494</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>44627</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44630</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45706</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>45432</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44903</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45602</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45328</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>44903</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>45251</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45121</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>45012</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>45071</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44617</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>45261</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44987</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>45747</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>45328</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45012</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45196</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45588</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>44944</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>45341</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>45600</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>45238</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>44987</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>45621</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>45600</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>44627</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>45551</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>45098</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>45128</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>45691</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>45482</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>45363</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45739</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45670</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44987</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>44987</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>45061</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>45432</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>45169</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>45201</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45201</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>45115</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>44908</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45310</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>45012</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45147</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>44880</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>44822</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>45426</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>45719</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>45440</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45169</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>44884</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>45299</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44754</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>45043</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>44600</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>45646</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>45402</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>45006</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>45099</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>45719</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>45754</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>45192</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45646</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>45225</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>45280</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>45714</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>45360</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>45559</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>45715</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>45560</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45670</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45932</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>45929</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45891</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45891</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>45673</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45440</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>46139</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45743</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45460</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>44939</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>45821</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45964</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>45888</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45889</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>45888</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45954</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45889</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45892</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>45757</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>45104</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>45889</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45903</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45889</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44966</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>46140</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>46140</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>46140</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>46140</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45280</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45280</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>45807</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>45706</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45104</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45841</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45749</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45743</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45843</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45807</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>45111</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45910</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>44848</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>45910</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>45915</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>45915</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>44916</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45915</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45915</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>45915</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>45915</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>45387</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>45918</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>45918</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>45505</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>46147</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45923</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45266</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>45616</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45053</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>45925</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>45706</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>46149</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>45429</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>46149</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>45597</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>45932</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45932</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>45932</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>45630</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45630</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>44944</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45019</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45937</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44722</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>44756</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45085</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45012</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45462</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>44966</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45947</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45272</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45950</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45299</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>45951</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>45432</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>45954</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>44966</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>45001</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>45001</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>45505</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>45359</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>45090</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45841</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>45589</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>45194</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>44917</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45168</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>45071</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45597</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>45197</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>45646</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>45099</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>45360</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>44565</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>46162</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>44980</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>44586</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>45974</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>45975</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>45610</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>45978</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>44595</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>44754</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>45978</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>44753</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>46162</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45166</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45001</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>46162</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>45646</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>45002</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>45981</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>45460</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>45246</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>45299</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>45001</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>45036</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>46164</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24951,7 +24951,7 @@
         <v>45986</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25024,7 +25024,7 @@
         <v>45986</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>45357</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>45054</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>44739</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45555</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45394</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>45581</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>45402</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>45992</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>45381</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>45169</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>45995</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45855</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>45354</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>46168</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>45009</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45009</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45702</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>46171</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>45588</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26499,7 +26499,7 @@
         <v>46007</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>46007</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26645,7 +26645,7 @@
         <v>45278</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>45602</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         <v>45754</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>44987</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>45117</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>45480</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>45302</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>45327</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>44729</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>45619</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>45714</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45337</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>44917</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>46182</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>46181</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27745,7 +27745,7 @@
         <v>46046</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>46048</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27891,7 +27891,7 @@
         <v>44778</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27964,7 +27964,7 @@
         <v>46050</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>44494</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>44973</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>44966</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>46052</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44489</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>46182</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>46052</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>46181</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>44762</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28709,7 +28709,7 @@
         <v>46059</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>46059</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28855,7 +28855,7 @@
         <v>46184</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>46184</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>44739</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>44753</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>44862</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29220,7 +29220,7 @@
         <v>46066</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29293,7 +29293,7 @@
         <v>45470</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>46071</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>45086</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>45310</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>45040</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>46073</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>46073</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>45757</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>46078</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>46078</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44829</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30111,7 +30111,7 @@
         <v>44956</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>46078</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>46078</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>46078</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>45166</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>46079</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>44882</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>45534</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>44893</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>45610</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>46086</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>46086</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30992,7 +30992,7 @@
         <v>44972</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31065,7 +31065,7 @@
         <v>44882</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>45009</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31211,7 +31211,7 @@
         <v>45062</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         <v>45316</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>45342</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         <v>44713</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>46104</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>46104</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>46104</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>46105</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45426</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>45588</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31951,7 +31951,7 @@
         <v>45194</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>46199</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>46104</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>45921</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>44817</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45559</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45328</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45328</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>45360</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>45360</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>46198</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45104</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>46119</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45105</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>44945</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>46126</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>46199</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33202,7 +33202,7 @@
         <v>46202</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44606</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>46202</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>45178</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>45068</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>45536</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>46133</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45072</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>45196</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>46062</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45625</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>45677</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45195</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>44992</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>46139</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>45811</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34375,7 +34375,7 @@
         <v>45082</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>45193</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34526,7 +34526,7 @@
         <v>45264</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45085</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>46210</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>45091</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>46209</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>46210</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>46209</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>46168</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>46212</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>46212</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>46140</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>45110</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35407,7 +35407,7 @@
         <v>46216</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45152</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45139</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45169</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>46209</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>46218</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45118</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>45178</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>45062</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>45201</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36142,7 +36142,7 @@
         <v>45195</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45027</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36288,7 +36288,7 @@
         <v>46226</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>45602</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>45378</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>45436</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>45350</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>45350</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>45303</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36799,7 +36799,7 @@
         <v>45303</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>46272</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36945,7 +36945,7 @@
         <v>46272</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>44974</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>44806</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>44992</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37237,7 +37237,7 @@
         <v>45246</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>46279</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>46279</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37466,7 +37466,7 @@
         <v>44565</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>45237</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37612,7 +37612,7 @@
         <v>44774</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>46276</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45545</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37831,7 +37831,7 @@
         <v>45303</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45430</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>44956</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>46281</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45342</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45342</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>45428</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45373</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>45724</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>44651</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>45560</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>45408</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>45097</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>45189</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38858,7 +38858,7 @@
         <v>45051</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         <v>45006</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45139</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39077,7 +39077,7 @@
         <v>46287</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>46287</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>45076</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>44819</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>44658</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>46287</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>45685</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39588,7 +39588,7 @@
         <v>45545</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39661,7 +39661,7 @@
         <v>45119</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>45201</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39807,7 +39807,7 @@
         <v>44992</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>45063</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39963,7 +39963,7 @@
         <v>44748</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>45078</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40109,7 +40109,7 @@
         <v>45327</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>45600</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44980</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>46247</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>44950</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>45722</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>46077</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>46292</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>45058</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>45560</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40859,7 +40859,7 @@
         <v>46248</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>46292</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45194</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>46079</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>45775</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41224,7 +41224,7 @@
         <v>45057</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>46042</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41370,7 +41370,7 @@
         <v>45012</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>45012</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>44902</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>45238</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>46253</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>46294</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41818,7 +41818,7 @@
         <v>46252</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>45545</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>45118</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45229</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>46300</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>45104</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>45104</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42344,7 +42344,7 @@
         <v>45574</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>45527</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>45531</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>45560</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45691</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>45394</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>45608</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>44966</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45104</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43006,7 +43006,7 @@
         <v>45502</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>46300</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>46298</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45785</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43303,7 +43303,7 @@
         <v>45567</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>46300</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>45527</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>45775</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>46261</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>45546</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45724</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43814,7 +43814,7 @@
         <v>45579</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43887,7 +43887,7 @@
         <v>45530</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>45646</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45562</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>46259</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>45551</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>46259</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>46181</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>45280</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>46302</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>46261</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44617,7 +44617,7 @@
         <v>45791</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>46112</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>45672</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>44973</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44919,7 +44919,7 @@
         <v>45078</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>45597</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45065,7 +45065,7 @@
         <v>45194</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>45247</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45579</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>45490</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>45803</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>45785</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>46265</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45581,7 +45581,7 @@
         <v>46265</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45654,7 +45654,7 @@
         <v>46265</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>46265</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45800,7 +45800,7 @@
         <v>46265</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>46311</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>46311</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45813</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46092,7 +46092,7 @@
         <v>46311</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>46311</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45413</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>46268</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46384,7 +46384,7 @@
         <v>46267</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
         <v>46267</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45827</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>46268</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45827</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46759,7 +46759,7 @@
         <v>46311</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>45825</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46905,7 +46905,7 @@
         <v>45833</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45835</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45835</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>45838</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>45838</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45840</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45843</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>45537</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45846</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45846</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45856</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45653</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>44474</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>44755</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44608</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>44986</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48078,7 +48078,7 @@
         <v>45485</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45646</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>45602</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>45573</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>45656</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>44959</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>45457</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45154</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45154</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>46050</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>46064</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>46099</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -601,7 +601,7 @@
         <v>43955</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45791</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44789</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44931</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45153</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45093</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>45471</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45103</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>44630</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>44762</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45594</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>44645</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>44762</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>45973</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>46071</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>46253</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>45230</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>44676</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>44655</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>45884</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>45588</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         <v>45741</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>46188</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>44998</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>44888</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>45152</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>44039</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>44657</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>44756</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>44957</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>45357</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>45194</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>44980</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>46175</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>46182</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>46181</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>46091</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>45559</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>46133</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>44973</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45717</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45012</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>45063</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>45559</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>46252</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>45457</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45699</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>45545</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>46099</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>46139</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>44546</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>44825</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>44649</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44880</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44630</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>44860</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>44880</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>44676</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>44510</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>44504</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>44848</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>44827</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44581</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44592</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44753</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44845</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>44790</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44608</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>44693</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>44860</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>44825</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         <v>44762</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>44825</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>44565</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>44503</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44490</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>44596</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>44576</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44721</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>44762</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>44762</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>44882</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>44532</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44494</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44518</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44806</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>44501</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>44845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>44872</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44630</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44886</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>44694</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>44504</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>44817</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44853</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>44638</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44812</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>44637</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44539</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44713</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44586</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44762</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         <v>44494</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>44627</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44630</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>45706</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>45432</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44903</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45602</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45328</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>44903</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>45251</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45121</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>45012</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>45071</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44617</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>45261</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44987</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>45747</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>45328</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45012</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45196</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45588</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>44944</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>45341</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>45600</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>45238</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>44987</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>45621</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>45600</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>44627</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>45551</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>45098</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>45128</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>45691</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>45482</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>45363</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45739</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45670</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44987</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>44987</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>45061</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12927,7 +12927,7 @@
         <v>45432</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>45169</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>45201</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>45201</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>45115</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>44908</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>45310</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>45012</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45147</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>44880</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>44822</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>45426</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>45719</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>45440</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45169</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>44884</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>45299</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44754</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>45043</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>44600</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>45646</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>45402</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>45006</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>45099</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>45719</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>45754</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>45192</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>45646</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>45225</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>45280</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>45714</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>45360</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>45559</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>45715</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>45560</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45670</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45932</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>45929</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45891</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45891</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>45673</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45440</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>46139</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45743</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45460</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>44939</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>45821</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45964</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>45888</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45889</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>45888</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45954</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45889</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45892</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>45757</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>45104</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>45889</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>45903</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45889</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44966</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>46140</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>46140</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>46140</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>46140</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45280</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45280</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>45807</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>45706</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45104</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45841</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45749</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45743</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45843</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45807</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>45111</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45910</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>44848</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>45910</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>45915</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>45915</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>44916</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45915</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45915</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>45915</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>45915</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>45387</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>45918</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>45918</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>45505</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>46147</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45923</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45266</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>45616</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45053</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>45925</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>45706</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>46149</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>45429</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>46149</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>45597</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>45932</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45932</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>45932</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>45630</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45630</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>44944</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45019</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45937</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44722</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>44756</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45085</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45012</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45462</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>44966</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45947</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45272</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45950</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45299</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>45951</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>45432</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>45954</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>44966</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21948,7 +21948,7 @@
         <v>45001</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>45001</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>45505</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>45359</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>45090</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45841</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>45589</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>45194</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>44917</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45168</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>45071</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45597</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>45197</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>45646</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>45099</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>45360</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>44565</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>46162</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>44980</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>44586</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>45974</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>45975</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>45610</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>45978</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>44595</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>44754</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23856,7 +23856,7 @@
         <v>45978</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>44753</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>46162</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45166</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45001</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>46162</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>45646</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>45002</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>45981</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>45460</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>45246</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>45299</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>45001</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24805,7 +24805,7 @@
         <v>45036</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>46164</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24951,7 +24951,7 @@
         <v>45986</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25024,7 +25024,7 @@
         <v>45986</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>45357</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>45054</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>44739</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45555</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45394</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>45581</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>45402</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>45992</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>45381</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>45169</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>45995</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45855</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>45354</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>46168</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>45009</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45009</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45702</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>46171</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>45588</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26499,7 +26499,7 @@
         <v>46007</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>46007</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26645,7 +26645,7 @@
         <v>45278</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>45602</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         <v>45754</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>44987</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>45117</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>45480</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>45302</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>45327</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>44729</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>45619</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>45714</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45337</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>44917</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>46182</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>46181</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27745,7 +27745,7 @@
         <v>46046</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>46048</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27891,7 +27891,7 @@
         <v>44778</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27964,7 +27964,7 @@
         <v>46050</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>44494</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>44973</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>44966</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>46052</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44489</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>46182</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>46052</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>46181</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>44762</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28709,7 +28709,7 @@
         <v>46059</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>46059</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28855,7 +28855,7 @@
         <v>46184</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>46184</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>44739</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>44753</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>44862</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29220,7 +29220,7 @@
         <v>46066</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29293,7 +29293,7 @@
         <v>45470</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>46071</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>45086</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>45310</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29590,7 +29590,7 @@
         <v>45040</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>46073</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>46073</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>45757</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>46078</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>46078</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44829</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30111,7 +30111,7 @@
         <v>44956</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>46078</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>46078</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>46078</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>45166</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>46079</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>44882</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>45534</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>44893</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>45610</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>46086</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>46086</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30992,7 +30992,7 @@
         <v>44972</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31065,7 +31065,7 @@
         <v>44882</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>45009</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31211,7 +31211,7 @@
         <v>45062</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         <v>45316</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>45342</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         <v>44713</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>46104</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>46104</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>46104</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>46105</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45426</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>45588</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31951,7 +31951,7 @@
         <v>45194</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>46199</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>46104</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>45921</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>44817</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45559</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45328</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45328</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>45360</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>45360</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>46198</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45104</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>46119</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45105</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>44945</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>46126</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>46199</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33202,7 +33202,7 @@
         <v>46202</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>44606</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>46202</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>45178</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>45068</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>45536</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>46133</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45072</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>45196</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>46062</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45625</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>45677</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45195</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>44992</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>46139</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>45811</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34375,7 +34375,7 @@
         <v>45082</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>45193</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34526,7 +34526,7 @@
         <v>45264</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45085</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>46210</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>45091</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>46209</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>46210</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>46209</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>46168</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>46212</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>46212</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>46140</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>45110</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35407,7 +35407,7 @@
         <v>46216</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45152</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45139</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45169</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>46209</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>46218</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45118</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>45178</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>45062</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>45201</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36142,7 +36142,7 @@
         <v>45195</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45027</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36288,7 +36288,7 @@
         <v>46226</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>45602</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>45378</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>45436</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>45350</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>45350</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>45303</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36799,7 +36799,7 @@
         <v>45303</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>46272</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36945,7 +36945,7 @@
         <v>46272</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>44974</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>44806</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>44992</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37237,7 +37237,7 @@
         <v>45246</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>46279</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>46279</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37466,7 +37466,7 @@
         <v>44565</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37539,7 +37539,7 @@
         <v>45237</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37612,7 +37612,7 @@
         <v>44774</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>46276</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45545</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37831,7 +37831,7 @@
         <v>45303</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45430</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>44956</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>46281</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45342</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45342</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>45428</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>45373</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38415,7 +38415,7 @@
         <v>45724</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>44651</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>45560</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>45408</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>45097</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>45189</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38858,7 +38858,7 @@
         <v>45051</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         <v>45006</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45139</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39077,7 +39077,7 @@
         <v>46287</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>46287</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>45076</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>44819</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>44658</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>46287</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>45685</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39588,7 +39588,7 @@
         <v>45545</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39661,7 +39661,7 @@
         <v>45119</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>45201</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39807,7 +39807,7 @@
         <v>44992</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>45063</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39963,7 +39963,7 @@
         <v>44748</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>45078</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40109,7 +40109,7 @@
         <v>45327</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>45600</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>44980</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>46247</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>44950</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>45722</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40557,7 +40557,7 @@
         <v>46077</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>46292</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>45058</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>45560</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40859,7 +40859,7 @@
         <v>46248</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>46292</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>45194</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>46079</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>45775</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41224,7 +41224,7 @@
         <v>45057</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>46042</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41370,7 +41370,7 @@
         <v>45012</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>45012</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>44902</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41589,7 +41589,7 @@
         <v>45238</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>46253</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>46294</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41818,7 +41818,7 @@
         <v>46252</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>45545</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>45118</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45229</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>46300</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>45104</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>45104</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42344,7 +42344,7 @@
         <v>45574</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>45527</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>45531</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>45560</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45691</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>45394</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>45608</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>44966</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45104</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43006,7 +43006,7 @@
         <v>45502</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>46300</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>46298</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45785</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43303,7 +43303,7 @@
         <v>45567</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>46300</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>45527</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>45775</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>46261</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>45546</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45724</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43814,7 +43814,7 @@
         <v>45579</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43887,7 +43887,7 @@
         <v>45530</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>45646</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45562</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>46259</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44179,7 +44179,7 @@
         <v>45551</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44252,7 +44252,7 @@
         <v>46259</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>46181</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>45280</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>46302</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>46261</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44617,7 +44617,7 @@
         <v>45791</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>46112</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>45672</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>44973</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44919,7 +44919,7 @@
         <v>45078</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>45597</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45065,7 +45065,7 @@
         <v>45194</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>45247</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45579</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>45490</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>45803</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>45785</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>46265</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45581,7 +45581,7 @@
         <v>46265</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45654,7 +45654,7 @@
         <v>46265</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>46265</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45800,7 +45800,7 @@
         <v>46265</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>46311</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>46311</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45813</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46092,7 +46092,7 @@
         <v>46311</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>46311</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45413</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>46268</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46384,7 +46384,7 @@
         <v>46267</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
         <v>46267</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45827</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>46268</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45827</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46759,7 +46759,7 @@
         <v>46311</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
         <v>45825</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46905,7 +46905,7 @@
         <v>45833</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45835</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45835</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>45838</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>45838</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45840</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45843</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>45537</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45846</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45846</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45856</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45653</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>44474</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>44755</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44608</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>44986</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48078,7 +48078,7 @@
         <v>45485</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45646</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>45602</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>45573</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>45656</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>44959</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>45457</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45154</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45154</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>46050</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>46064</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>46099</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -601,7 +601,7 @@
         <v>43955</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45791</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44789</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44931</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>45153</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>45103</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45471</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45093</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>44630</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>45594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>46317</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>44762</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>44762</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>46071</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>46253</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45973</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>45230</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>44676</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45884</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>46188</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45741</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>44655</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>44998</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>44888</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>45152</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45588</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>44039</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>44657</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>44756</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>46175</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>44957</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>45559</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>46181</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>46182</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45717</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>45457</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>45699</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45545</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>46252</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>46091</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>46133</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>46317</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>46317</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>44973</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>45012</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45357</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>45559</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>45063</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>45194</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>44980</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>46099</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>46139</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44546</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44825</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44649</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>44880</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>44630</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44860</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>44880</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>44676</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>44510</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>44504</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>44848</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44827</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>44581</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>44592</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>44753</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>44845</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>44790</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>44608</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44860</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44693</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>44825</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44762</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>44825</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>44503</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>44565</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44596</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>44576</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>44721</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44762</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>44762</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>44882</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>44532</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>44494</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>44806</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>44501</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>44518</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>44845</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>44872</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>44886</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>44630</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>44694</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>44504</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>44817</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>44853</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>44638</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>44812</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>44637</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>44539</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10037,7 +10037,7 @@
         <v>44713</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>44586</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>44762</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>45006</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>44494</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>45888</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44627</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>45757</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>44630</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>45621</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>45201</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45195</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>45051</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>45719</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>45402</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>45889</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>45196</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>44778</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45888</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45889</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>45139</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>45892</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>44617</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>44987</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>45360</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>45536</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>45272</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>45062</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>45111</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>45545</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>44939</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>45363</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>45807</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>45006</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>45082</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>45342</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>45342</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>45841</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>45749</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>45743</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>45807</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>45910</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45843</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45910</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>45646</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>46162</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>45012</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>45012</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>45246</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>45841</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>46162</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>46162</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>45915</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>45057</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>45915</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>45915</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>45915</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>46164</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45915</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>45915</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>45918</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45063</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>45918</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44739</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45104</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45560</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>45105</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>46168</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15076,7 +15076,7 @@
         <v>45310</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>44893</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>45378</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>45923</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>44806</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>45001</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>44974</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>45925</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>45706</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45602</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>45932</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>45932</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>46171</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>45932</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>44722</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>45394</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>44902</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>45373</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>45937</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>45359</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
         <v>45360</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>44754</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>45072</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>45238</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>45426</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45053</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>45381</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45097</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>45754</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>46182</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45086</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>45947</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45950</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45462</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44956</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>46181</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>46181</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45951</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>46182</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>45058</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45954</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         <v>45327</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>45402</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>46184</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>45012</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>45012</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>44756</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>46184</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>45261</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>45098</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45337</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>45360</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>45974</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>45921</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>46198</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>45714</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>45978</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>45975</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>46199</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>45978</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45001</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>46202</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>46199</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>45121</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>45350</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>45350</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>45545</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>44774</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>45169</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>46202</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>45714</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45981</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>45630</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>45630</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45588</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44908</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45430</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>45986</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45986</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>45408</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>45610</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>45505</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>44973</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45278</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45019</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>46209</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>46209</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>45036</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>46140</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45119</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>45992</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45229</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45600</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>46210</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>46210</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>46168</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>46212</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>46212</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45040</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>44903</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45099</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>44950</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45855</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>46216</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45995</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45043</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>46218</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>46209</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44884</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>45685</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45357</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>44972</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>45560</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45531</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45394</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45104</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>45574</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>45104</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>45691</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45608</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>45502</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>44966</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>45527</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>46226</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>45567</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>46007</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>46007</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>46279</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45785</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>45724</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>45551</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>45579</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>45530</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>45562</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>45527</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>46281</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45646</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45280</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45546</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>44817</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45791</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>46287</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>46287</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>46048</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>45597</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>45672</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>46046</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44973</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>45194</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>46287</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45078</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>46050</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45247</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>46052</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45775</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>45579</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>45803</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>46042</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>46077</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>46052</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45490</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>46079</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>45785</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>46247</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27143,7 +27143,7 @@
         <v>45328</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>46294</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>46059</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27367,7 +27367,7 @@
         <v>46059</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>45813</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>46248</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27586,7 +27586,7 @@
         <v>46066</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>46292</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>46292</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>46071</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>46253</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>46073</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>45413</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>46073</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>46078</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>46078</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>46078</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>46252</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>46079</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>46078</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45825</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>46078</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45827</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45827</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>46086</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>46300</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>46086</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>44595</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>45833</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>45838</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29373,7 +29373,7 @@
         <v>45838</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29446,7 +29446,7 @@
         <v>45835</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>45835</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>46300</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45840</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>46300</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29811,7 +29811,7 @@
         <v>45846</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>44944</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45118</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>45846</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>46298</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>45537</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>45843</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45012</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>46105</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>46104</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>44980</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>46104</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>46104</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>46259</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30838,7 +30838,7 @@
         <v>46259</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>46302</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>46104</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         <v>45856</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>46119</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>45653</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>46261</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>46261</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45775</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>45619</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>46126</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>46181</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>45303</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>45715</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>46133</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>46265</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>45597</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>45646</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>46265</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>46265</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>46265</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45811</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45426</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>45280</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45589</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>44992</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45964</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>45677</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>45559</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45932</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>46265</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>45821</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>46112</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>45673</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33340,7 +33340,7 @@
         <v>45903</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>45929</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33486,7 +33486,7 @@
         <v>45560</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>46268</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33637,7 +33637,7 @@
         <v>45440</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>44903</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>45625</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>44992</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33934,7 +33934,7 @@
         <v>45954</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>45387</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>46268</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>45670</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34226,7 +34226,7 @@
         <v>45889</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>44627</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>45889</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>44966</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>45616</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45178</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45602</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>46267</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>46267</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>46311</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>46311</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>45551</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35112,7 +35112,7 @@
         <v>46140</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>46311</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>46311</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>46140</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>46311</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>45891</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>45891</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>44565</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>46139</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>45104</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>46062</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>45505</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>45706</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>46272</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>46316</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>45192</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>45194</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36368,7 +36368,7 @@
         <v>46316</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36441,7 +36441,7 @@
         <v>46316</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>46316</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>46140</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>46272</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>46139</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>46316</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>46140</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>46315</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>46316</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45197</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>46317</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>45722</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>46276</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>46279</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
         <v>46317</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>46317</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>46317</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>46317</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>46317</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>45588</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>46317</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>44944</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>46317</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>45071</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
         <v>45054</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>46147</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45238</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>46149</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>45091</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>46149</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>44754</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45739</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38847,7 +38847,7 @@
         <v>45559</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45068</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>45280</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39071,7 +39071,7 @@
         <v>45085</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>45009</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>45009</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>45012</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>44966</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39441,7 +39441,7 @@
         <v>45299</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>45328</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>45328</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>45009</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45480</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>45328</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>45061</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>44713</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45166</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45001</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>45646</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40244,7 +40244,7 @@
         <v>45178</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40317,7 +40317,7 @@
         <v>45757</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>45117</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40463,7 +40463,7 @@
         <v>44822</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40536,7 +40536,7 @@
         <v>44987</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44739</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45482</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>45085</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>45193</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>45194</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40974,7 +40974,7 @@
         <v>45555</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         <v>44748</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45743</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41198,7 +41198,7 @@
         <v>45754</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41271,7 +41271,7 @@
         <v>44916</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41344,7 +41344,7 @@
         <v>44862</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>45264</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>44917</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>45090</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>44882</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41714,7 +41714,7 @@
         <v>45266</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41792,7 +41792,7 @@
         <v>44880</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45196</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>45600</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45436</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>44966</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45303</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>45303</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45194</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>45341</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>45168</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42522,7 +42522,7 @@
         <v>45342</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>45139</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
         <v>45104</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45110</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>45147</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45602</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42960,7 +42960,7 @@
         <v>45062</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43038,7 +43038,7 @@
         <v>44753</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45002</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43184,7 +43184,7 @@
         <v>45078</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43257,7 +43257,7 @@
         <v>45429</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>45152</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>45581</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>44494</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43549,7 +43549,7 @@
         <v>45706</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45104</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>45460</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45719</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>45115</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>45316</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45545</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>45670</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44143,7 +44143,7 @@
         <v>45588</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>45534</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45118</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>45600</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44440,7 +44440,7 @@
         <v>45610</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45169</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>45747</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44659,7 +44659,7 @@
         <v>45169</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>45076</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44805,7 +44805,7 @@
         <v>44606</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>44829</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>44762</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>44658</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>45646</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>44565</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45248,7 +45248,7 @@
         <v>45691</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45201</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>44600</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45467,7 +45467,7 @@
         <v>45440</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45540,7 +45540,7 @@
         <v>45432</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>45428</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45432</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>44586</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>44753</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>45237</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>44729</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45246</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45702</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>45201</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46270,7 +46270,7 @@
         <v>45724</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46343,7 +46343,7 @@
         <v>45251</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>44819</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46494,7 +46494,7 @@
         <v>45195</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46567,7 +46567,7 @@
         <v>44882</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>45169</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>45299</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>45189</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>45460</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45299</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47005,7 +47005,7 @@
         <v>45302</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45099</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47151,7 +47151,7 @@
         <v>45310</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
         <v>44987</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>45201</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>45071</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>45597</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>45128</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47589,7 +47589,7 @@
         <v>45560</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>44848</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>45432</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>44956</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>44987</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>44987</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48032,7 +48032,7 @@
         <v>45470</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>45360</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48178,7 +48178,7 @@
         <v>45225</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45327</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48324,7 +48324,7 @@
         <v>45354</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48397,7 +48397,7 @@
         <v>45027</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48470,7 +48470,7 @@
         <v>44980</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45280</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>44917</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48694,7 +48694,7 @@
         <v>45166</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48767,7 +48767,7 @@
         <v>44651</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>44966</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48913,7 +48913,7 @@
         <v>45001</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48986,7 +48986,7 @@
         <v>44945</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>44992</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>44474</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49205,7 +49205,7 @@
         <v>44755</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49278,7 +49278,7 @@
         <v>44608</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>44986</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49429,7 +49429,7 @@
         <v>45485</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49502,7 +49502,7 @@
         <v>45646</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49575,7 +49575,7 @@
         <v>45602</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49648,7 +49648,7 @@
         <v>45573</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>45656</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49794,7 +49794,7 @@
         <v>44959</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49867,7 +49867,7 @@
         <v>45457</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
         <v>45154</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>45154</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>46050</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>46064</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50237,7 +50237,7 @@
         <v>46099</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>

--- a/Översikt RONNEBY.xlsx
+++ b/Översikt RONNEBY.xlsx
@@ -601,7 +601,7 @@
         <v>43955</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>45791</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         <v>44789</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44931</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>45153</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>45103</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45471</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45093</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>44630</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>45594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>46317</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>44762</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44645</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>44762</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>46071</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>46253</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45973</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>45230</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>44676</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>45884</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>46188</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>45741</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>44655</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>44998</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>44888</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>45152</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45588</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>44039</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>44657</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>44756</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>46175</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>44957</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>45559</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>46181</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>46182</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45717</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>45457</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>45699</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45545</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>46252</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>46091</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>46133</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>46317</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>46317</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>44973</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>45012</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45357</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>45559</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>45063</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>45194</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>44980</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>46099</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>46139</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44546</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44825</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44649</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>44880</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>44630</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44860</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>44880</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>44676</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>44510</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
         <v>44504</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>44848</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>44827</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>44581</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>44592</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>44753</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>44845</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>44790</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>44608</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44860</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>44693</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>44825</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44762</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>44825</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>44503</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>44565</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>44596</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>44576</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>44721</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44762</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>44762</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>44882</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>44532</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>44494</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>44806</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>44501</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>44518</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>44845</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>44872</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>44886</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>44630</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>44694</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>44504</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>44817</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>44853</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>44638</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>44812</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>44637</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>44539</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10037,7 +10037,7 @@
         <v>44713</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>44586</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>44762</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>45006</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>44494</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>45888</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44627</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>45757</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>44630</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>45621</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>45201</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45195</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>45051</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>45719</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>45402</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>45889</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>45196</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>44778</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45888</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45889</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>45139</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>45892</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>44617</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>44987</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>45360</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>45536</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>45272</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>45062</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>45111</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>45545</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>44939</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>45363</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>45807</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>45006</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>45082</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>45342</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>45342</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>45841</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>45749</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>45743</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>45807</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>45910</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45843</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45910</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>45646</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>46162</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>45012</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>45012</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>45246</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>45841</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>46162</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>46162</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>45915</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>45057</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>45915</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>45915</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>45915</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>46164</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45915</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>45915</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>45918</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45063</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>45918</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44739</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45104</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45560</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>45105</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>46168</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15076,7 +15076,7 @@
         <v>45310</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>44893</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>45378</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>45923</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>44806</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>45001</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>44974</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>45925</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>45706</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45602</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>45932</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>45932</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>46171</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>45932</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>44722</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>45394</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>44902</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>45373</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>45937</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>45359</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
         <v>45360</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>44754</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>45072</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>45238</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>45426</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45053</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>45381</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45097</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>45754</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>46182</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>45086</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>45947</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17437,7 +17437,7 @@
         <v>45950</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45462</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>44956</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>46181</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>46181</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45951</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>46182</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>45058</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>45954</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         <v>45327</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>45402</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>46184</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>45012</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>45012</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>44756</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>46184</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>45261</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>45098</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45337</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>45360</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>45974</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>45921</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>46198</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>45714</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>45978</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>45975</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>46199</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>45978</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45001</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>46202</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19632,7 +19632,7 @@
         <v>46199</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>45121</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>45350</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>45350</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>45545</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>44774</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>45169</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>46202</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>45714</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45981</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>45630</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>45630</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45588</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>44908</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45430</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>45986</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45986</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>45408</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>45610</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>45505</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>44973</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45278</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45019</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>46209</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>46209</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>45036</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>46140</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45119</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>45992</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45229</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45600</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>46210</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>46210</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>46168</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>46212</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>46212</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45040</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>44903</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45099</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>44950</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45855</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>46216</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45995</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45043</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>46218</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>46209</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44884</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>45685</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45357</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>44972</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>45560</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45531</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45394</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45104</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>45574</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>45104</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>45691</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45608</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>45502</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>44966</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>45527</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>46226</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>45567</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>46007</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>46007</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>46279</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45785</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>45724</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>45551</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>45579</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>45530</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>45562</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>45527</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>46281</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45646</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45280</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45546</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>44817</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45791</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>46287</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>46287</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>46048</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>45597</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>45672</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>46046</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44973</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>45194</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>46287</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45078</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>46050</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45247</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>46052</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45775</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>45579</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>45803</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>46042</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         <v>46077</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>46052</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45490</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>46079</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>45785</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>46247</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27143,7 +27143,7 @@
         <v>45328</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>46294</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>46059</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27367,7 +27367,7 @@
         <v>46059</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>45813</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>46248</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27586,7 +27586,7 @@
         <v>46066</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>46292</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>46292</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>46071</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>46253</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>46073</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>45413</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>46073</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>46078</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>46078</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>46078</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>46252</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>46079</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>46078</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45825</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>46078</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45827</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45827</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>46086</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>46300</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>46086</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>44595</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>45833</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>45838</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29373,7 +29373,7 @@
         <v>45838</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29446,7 +29446,7 @@
         <v>45835</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>45835</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29592,7 +29592,7 @@
         <v>46300</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45840</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>46300</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29811,7 +29811,7 @@
         <v>45846</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>44944</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>45118</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>45846</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>46298</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         <v>45537</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>45843</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30322,7 +30322,7 @@
         <v>45012</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>46105</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>46104</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>44980</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>46104</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>46104</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>46259</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30838,7 +30838,7 @@
         <v>46259</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>46302</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>46104</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         <v>45856</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>46119</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>45653</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>46261</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>46261</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45775</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>45619</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>46126</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>46181</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>45303</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>45715</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>46133</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>46265</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>45597</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>45646</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>46265</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>46265</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>46265</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45811</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45426</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>45280</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45589</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>44992</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>45964</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>45677</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>45559</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45932</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>46265</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>45821</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>46112</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>45673</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33340,7 +33340,7 @@
         <v>45903</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>45929</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33486,7 +33486,7 @@
         <v>45560</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>46268</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33637,7 +33637,7 @@
         <v>45440</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>44903</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>45625</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>44992</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33934,7 +33934,7 @@
         <v>45954</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>45387</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>46268</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>45670</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34226,7 +34226,7 @@
         <v>45889</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>44627</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>45889</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>44966</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>45616</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45178</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45602</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>46267</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>46267</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34893,7 +34893,7 @@
         <v>46311</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>46311</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>45551</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35112,7 +35112,7 @@
         <v>46140</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>46311</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>46311</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>46140</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>46311</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>45891</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>45891</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>44565</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>46139</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>45104</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>46062</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>45505</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>45706</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>46272</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>46316</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>45192</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>45194</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36368,7 +36368,7 @@
         <v>46316</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36441,7 +36441,7 @@
         <v>46316</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>46316</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>46140</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>46272</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>46139</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>46316</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>46140</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>46315</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>46316</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45197</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>46317</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>45722</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>46276</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>46279</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
         <v>46317</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>46317</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>46317</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>46317</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>46317</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>45588</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>46317</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>44944</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>46317</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38190,7 +38190,7 @@
         <v>45071</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
         <v>45054</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>46147</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45238</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>46149</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>45091</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>46149</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>44754</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45739</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38847,7 +38847,7 @@
         <v>45559</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45068</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>45280</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39071,7 +39071,7 @@
         <v>45085</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>45009</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>45009</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>45012</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>44966</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39441,7 +39441,7 @@
         <v>45299</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>45328</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>45328</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>45009</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45480</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>45328</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>45061</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>44713</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45166</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45001</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>45646</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40244,7 +40244,7 @@
         <v>45178</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40317,7 +40317,7 @@
         <v>45757</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>45117</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40463,7 +40463,7 @@
         <v>44822</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40536,7 +40536,7 @@
         <v>44987</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44739</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45482</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>45085</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>45193</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>45194</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40974,7 +40974,7 @@
         <v>45555</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         <v>44748</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45743</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41198,7 +41198,7 @@
         <v>45754</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41271,7 +41271,7 @@
         <v>44916</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41344,7 +41344,7 @@
         <v>44862</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>45264</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>44917</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>45090</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>44882</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41714,7 +41714,7 @@
         <v>45266</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41792,7 +41792,7 @@
         <v>44880</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45196</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>45600</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45436</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>44966</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45303</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>45303</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45194</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>45341</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>45168</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42522,7 +42522,7 @@
         <v>45342</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>45139</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
         <v>45104</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45110</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>45147</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45602</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42960,7 +42960,7 @@
         <v>45062</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43038,7 +43038,7 @@
         <v>44753</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45002</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43184,7 +43184,7 @@
         <v>45078</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43257,7 +43257,7 @@
         <v>45429</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>45152</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>45581</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>44494</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43549,7 +43549,7 @@
         <v>45706</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45104</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>45460</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45719</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>45115</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>45316</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         <v>45545</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44070,7 +44070,7 @@
         <v>45670</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44143,7 +44143,7 @@
         <v>45588</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>45534</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45118</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>45600</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44440,7 +44440,7 @@
         <v>45610</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45169</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>45747</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44659,7 +44659,7 @@
         <v>45169</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>45076</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44805,7 +44805,7 @@
         <v>44606</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>44829</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>44762</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>44658</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>45646</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>44565</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45248,7 +45248,7 @@
         <v>45691</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45201</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>44600</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45467,7 +45467,7 @@
         <v>45440</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45540,7 +45540,7 @@
         <v>45432</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>45428</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45432</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>44586</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>44753</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>45237</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>44729</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>45246</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45702</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>45201</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46270,7 +46270,7 @@
         <v>45724</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46343,7 +46343,7 @@
         <v>45251</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>44819</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46494,7 +46494,7 @@
         <v>45195</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46567,7 +46567,7 @@
         <v>44882</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>45169</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>45299</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>45189</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>45460</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
         <v>45299</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47005,7 +47005,7 @@
         <v>45302</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47078,7 +47078,7 @@
         <v>45099</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47151,7 +47151,7 @@
         <v>45310</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
         <v>44987</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>45201</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>45071</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>45597</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>45128</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47589,7 +47589,7 @@
         <v>45560</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>44848</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47740,7 +47740,7 @@
         <v>45432</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>44956</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>44987</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>44987</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48032,7 +48032,7 @@
         <v>45470</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>45360</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48178,7 +48178,7 @@
         <v>45225</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45327</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48324,7 +48324,7 @@
         <v>45354</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48397,7 +48397,7 @@
         <v>45027</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48470,7 +48470,7 @@
         <v>44980</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45280</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>44917</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48694,7 +48694,7 @@
         <v>45166</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48767,7 +48767,7 @@
         <v>44651</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>44966</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48913,7 +48913,7 @@
         <v>45001</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48986,7 +48986,7 @@
         <v>44945</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>44992</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>44474</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49205,7 +49205,7 @@
         <v>44755</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49278,7 +49278,7 @@
         <v>44608</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>44986</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49429,7 +49429,7 @@
         <v>45485</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49502,7 +49502,7 @@
         <v>45646</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49575,7 +49575,7 @@
         <v>45602</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49648,7 +49648,7 @@
         <v>45573</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>45656</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49794,7 +49794,7 @@
         <v>44959</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49867,7 +49867,7 @@
         <v>45457</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
         <v>45154</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>45154</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>46050</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>46064</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50237,7 +50237,7 @@
         <v>46099</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
